--- a/research/traditional_assets/database/data/spain/spain_education.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_education.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="bme_pro" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,80 +589,113 @@
           <t>Education</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.254</v>
+      </c>
+      <c r="E2">
+        <v>0.392</v>
+      </c>
+      <c r="G2">
+        <v>0.21276886035313</v>
+      </c>
+      <c r="H2">
+        <v>0.2126805778491172</v>
+      </c>
+      <c r="I2">
+        <v>0.198137215525471</v>
+      </c>
+      <c r="J2">
+        <v>0.1361666396058024</v>
+      </c>
       <c r="K2">
-        <v>0</v>
+        <v>32.2</v>
+      </c>
+      <c r="L2">
+        <v>0.1292134831460674</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>36.43</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.03792816241540864</v>
+      </c>
+      <c r="O2">
+        <v>1.131366459627329</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>36.2</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.03768870380010412</v>
+      </c>
+      <c r="R2">
+        <v>1.124223602484472</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.2299999999999969</v>
+      </c>
+      <c r="T2">
+        <v>0.006313477902827254</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>46.2</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.04809994794377929</v>
+      </c>
+      <c r="W2">
+        <v>1.457013574660633</v>
       </c>
       <c r="X2">
-        <v>0.07159011821159149</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>-0.01540511921986016</v>
+        <v>0.1084223527953934</v>
+      </c>
+      <c r="Y2">
+        <v>1.34859122186524</v>
       </c>
       <c r="AB2">
-        <v>0.07087236568034642</v>
-      </c>
-      <c r="AC2">
-        <v>-0.08627748490020659</v>
+        <v>0.1077553528123612</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.257</v>
       </c>
       <c r="AE2">
-        <v>17.60612204555599</v>
+        <v>12.82102945526309</v>
       </c>
       <c r="AF2">
-        <v>17.60612204555599</v>
+        <v>13.07802945526309</v>
       </c>
       <c r="AG2">
-        <v>17.60612204555599</v>
+        <v>-33.12197054473692</v>
       </c>
       <c r="AH2">
-        <v>0.01881787819757204</v>
+        <v>0.01343295458565403</v>
       </c>
       <c r="AI2">
-        <v>1</v>
+        <v>0.4276936639882822</v>
       </c>
       <c r="AJ2">
-        <v>0.01881787819757204</v>
+        <v>-0.03571571623730679</v>
       </c>
       <c r="AK2">
-        <v>1</v>
+        <v>2.120217193463842</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.101</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-0.409</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>0.004618979151689432</v>
+      </c>
+      <c r="AO2">
+        <v>488.118811881188</v>
       </c>
       <c r="AP2">
-        <v>5.417268321709536</v>
+        <v>-0.5952906280506276</v>
+      </c>
+      <c r="AQ2">
+        <v>-120.5378973105134</v>
       </c>
     </row>
     <row r="3">
@@ -679,80 +714,8825 @@
           <t>Education</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.254</v>
+      </c>
+      <c r="E3">
+        <v>0.392</v>
+      </c>
+      <c r="G3">
+        <v>0.21276886035313</v>
+      </c>
+      <c r="H3">
+        <v>0.2126805778491172</v>
+      </c>
+      <c r="I3">
+        <v>0.198137215525471</v>
+      </c>
+      <c r="J3">
+        <v>0.1361666396058024</v>
+      </c>
       <c r="K3">
-        <v>0</v>
+        <v>32.2</v>
+      </c>
+      <c r="L3">
+        <v>0.1292134831460674</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>36.43</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03792816241540864</v>
+      </c>
+      <c r="O3">
+        <v>1.131366459627329</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>36.2</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.03768870380010412</v>
+      </c>
+      <c r="R3">
+        <v>1.124223602484472</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.2299999999999969</v>
+      </c>
+      <c r="T3">
+        <v>0.006313477902827254</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>46.2</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.04809994794377929</v>
+      </c>
+      <c r="W3">
+        <v>1.457013574660633</v>
       </c>
       <c r="X3">
-        <v>0.07159011821159149</v>
+        <v>0.1084223527953934</v>
+      </c>
+      <c r="Y3">
+        <v>1.34859122186524</v>
+      </c>
+      <c r="AB3">
+        <v>0.1077553528123612</v>
+      </c>
+      <c r="AD3">
+        <v>0.257</v>
+      </c>
+      <c r="AE3">
+        <v>12.82102945526309</v>
+      </c>
+      <c r="AF3">
+        <v>13.07802945526309</v>
+      </c>
+      <c r="AG3">
+        <v>-33.12197054473692</v>
+      </c>
+      <c r="AH3">
+        <v>0.01343295458565403</v>
+      </c>
+      <c r="AI3">
+        <v>0.4276936639882822</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.03571571623730679</v>
+      </c>
+      <c r="AK3">
+        <v>2.120217193463842</v>
+      </c>
+      <c r="AL3">
+        <v>0.101</v>
+      </c>
+      <c r="AM3">
+        <v>-0.409</v>
+      </c>
+      <c r="AN3">
+        <v>0.004618979151689432</v>
+      </c>
+      <c r="AO3">
+        <v>488.118811881188</v>
+      </c>
+      <c r="AP3">
+        <v>-0.5952906280506276</v>
+      </c>
+      <c r="AQ3">
+        <v>-120.5378973105134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Proeduca Altus, S.A. (BME:PRO)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BME:PRO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.013432954585654</v>
+      </c>
+      <c r="F2">
+        <v>0.21</v>
+      </c>
+      <c r="G2">
+        <v>960.5</v>
+      </c>
+      <c r="H2">
+        <v>813.378719085831</v>
+      </c>
+      <c r="I2">
+        <v>927.378029455263</v>
+      </c>
+      <c r="J2">
+        <v>971.6301052714369</v>
+      </c>
+      <c r="K2">
+        <v>13.0780294552631</v>
+      </c>
+      <c r="L2">
+        <v>204.451386185605</v>
+      </c>
+      <c r="M2">
+        <v>0.107755352812361</v>
+      </c>
+      <c r="N2">
+        <v>0.10461483927328</v>
+      </c>
+      <c r="O2">
+        <v>0.0587683486238532</v>
+      </c>
+      <c r="P2">
+        <v>0.04125</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.108422352795393</v>
+      </c>
+      <c r="T2">
+        <v>0.12145865730795</v>
+      </c>
+      <c r="U2">
+        <v>0.8027379026742441</v>
+      </c>
+      <c r="V2">
+        <v>0.953045028516229</v>
+      </c>
+      <c r="W2">
+        <v>4.532751232539799</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>960.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.08673111430699013</v>
+      </c>
+      <c r="AC2">
+        <v>0.07835779816513762</v>
+      </c>
+      <c r="AD2">
+        <v>0.25</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>55.64</v>
+      </c>
+      <c r="AH2">
+        <v>4.67</v>
+      </c>
+      <c r="AI2">
+        <v>4.703999999999999</v>
+      </c>
+      <c r="AJ2">
+        <v>13.07802945526309</v>
+      </c>
+      <c r="AK2">
+        <v>0.2569999999999997</v>
+      </c>
+      <c r="AL2">
+        <v>0.101</v>
+      </c>
+      <c r="AM2">
+        <v>0.2569999999999997</v>
+      </c>
+      <c r="AN2">
+        <v>46.2</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1077185638768129</v>
+      </c>
+      <c r="C2">
+        <v>974.0730666213816</v>
+      </c>
+      <c r="D2">
+        <v>927.8730666213816</v>
+      </c>
+      <c r="E2">
+        <v>-13.07802945526309</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>46.2</v>
+      </c>
+      <c r="H2">
+        <v>960.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>55.64</v>
+      </c>
+      <c r="K2">
+        <v>4.67</v>
+      </c>
+      <c r="L2">
+        <v>50.97</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>50.97</v>
+      </c>
+      <c r="O2">
+        <v>12.7425</v>
+      </c>
+      <c r="P2">
+        <v>38.2275</v>
+      </c>
+      <c r="Q2">
+        <v>42.8975</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1077185638768129</v>
+      </c>
+      <c r="T2">
+        <v>0.7946232955438741</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.034275</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1075010174671209</v>
+      </c>
+      <c r="C3">
+        <v>967.2754590313308</v>
+      </c>
+      <c r="D3">
+        <v>930.8112393258834</v>
+      </c>
+      <c r="E3">
+        <v>-3.342249160710455</v>
+      </c>
+      <c r="F3">
+        <v>9.735780294552631</v>
+      </c>
+      <c r="G3">
+        <v>46.2</v>
+      </c>
+      <c r="H3">
+        <v>960.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>55.64</v>
+      </c>
+      <c r="K3">
+        <v>4.67</v>
+      </c>
+      <c r="L3">
+        <v>50.97</v>
+      </c>
+      <c r="M3">
+        <v>0.4449251594610553</v>
+      </c>
+      <c r="N3">
+        <v>50.52507484053894</v>
+      </c>
+      <c r="O3">
+        <v>12.63126871013474</v>
+      </c>
+      <c r="P3">
+        <v>37.89380613040421</v>
+      </c>
+      <c r="Q3">
+        <v>42.56380613040421</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.108240674209213</v>
+      </c>
+      <c r="T3">
+        <v>0.800643168994964</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.034275</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>114.5585924197695</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
-      <c r="AA3">
-        <v>-0.01540511921986016</v>
-      </c>
-      <c r="AB3">
-        <v>0.07087236568034642</v>
-      </c>
-      <c r="AC3">
-        <v>-0.08627748490020659</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>17.60612204555599</v>
-      </c>
-      <c r="AF3">
-        <v>17.60612204555599</v>
-      </c>
-      <c r="AG3">
-        <v>17.60612204555599</v>
-      </c>
-      <c r="AH3">
-        <v>0.01881787819757204</v>
-      </c>
-      <c r="AI3">
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1072834710574289</v>
+      </c>
+      <c r="C4">
+        <v>960.4965183958915</v>
+      </c>
+      <c r="D4">
+        <v>933.7680789849967</v>
+      </c>
+      <c r="E4">
+        <v>6.393531133842176</v>
+      </c>
+      <c r="F4">
+        <v>19.47156058910526</v>
+      </c>
+      <c r="G4">
+        <v>46.2</v>
+      </c>
+      <c r="H4">
+        <v>960.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>55.64</v>
+      </c>
+      <c r="K4">
+        <v>4.67</v>
+      </c>
+      <c r="L4">
+        <v>50.97</v>
+      </c>
+      <c r="M4">
+        <v>0.8898503189221106</v>
+      </c>
+      <c r="N4">
+        <v>50.08014968107789</v>
+      </c>
+      <c r="O4">
+        <v>12.52003742026947</v>
+      </c>
+      <c r="P4">
+        <v>37.56011226080842</v>
+      </c>
+      <c r="Q4">
+        <v>42.23011226080842</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1087734398545193</v>
+      </c>
+      <c r="T4">
+        <v>0.8067858970062805</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.034275</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>57.27929620988476</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1070659246477368</v>
+      </c>
+      <c r="C5">
+        <v>953.7364231757952</v>
+      </c>
+      <c r="D5">
+        <v>936.743764059453</v>
+      </c>
+      <c r="E5">
+        <v>16.12931142839481</v>
+      </c>
+      <c r="F5">
+        <v>29.20734088365789</v>
+      </c>
+      <c r="G5">
+        <v>46.2</v>
+      </c>
+      <c r="H5">
+        <v>960.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>55.64</v>
+      </c>
+      <c r="K5">
+        <v>4.67</v>
+      </c>
+      <c r="L5">
+        <v>50.97</v>
+      </c>
+      <c r="M5">
+        <v>1.334775478383166</v>
+      </c>
+      <c r="N5">
+        <v>49.63522452161683</v>
+      </c>
+      <c r="O5">
+        <v>12.40880613040421</v>
+      </c>
+      <c r="P5">
+        <v>37.22641839121263</v>
+      </c>
+      <c r="Q5">
+        <v>41.89641839121263</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1093171903584916</v>
+      </c>
+      <c r="T5">
+        <v>0.8130552792033969</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.034275</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>38.18619747325651</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1068483782380448</v>
+      </c>
+      <c r="C6">
+        <v>946.9953541138843</v>
+      </c>
+      <c r="D6">
+        <v>939.7384752920948</v>
+      </c>
+      <c r="E6">
+        <v>25.86509172294744</v>
+      </c>
+      <c r="F6">
+        <v>38.94312117821053</v>
+      </c>
+      <c r="G6">
+        <v>46.2</v>
+      </c>
+      <c r="H6">
+        <v>960.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>55.64</v>
+      </c>
+      <c r="K6">
+        <v>4.67</v>
+      </c>
+      <c r="L6">
+        <v>50.97</v>
+      </c>
+      <c r="M6">
+        <v>1.779700637844221</v>
+      </c>
+      <c r="N6">
+        <v>49.19029936215578</v>
+      </c>
+      <c r="O6">
+        <v>12.29757484053894</v>
+      </c>
+      <c r="P6">
+        <v>36.89272452161683</v>
+      </c>
+      <c r="Q6">
+        <v>41.56272452161684</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1098722689979633</v>
+      </c>
+      <c r="T6">
+        <v>0.8194552735296202</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.034275</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>28.63964810494238</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1066308318283528</v>
+      </c>
+      <c r="C7">
+        <v>940.2734942717094</v>
+      </c>
+      <c r="D7">
+        <v>942.7523957444726</v>
+      </c>
+      <c r="E7">
+        <v>35.60087201750007</v>
+      </c>
+      <c r="F7">
+        <v>48.67890147276316</v>
+      </c>
+      <c r="G7">
+        <v>46.2</v>
+      </c>
+      <c r="H7">
+        <v>960.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>55.64</v>
+      </c>
+      <c r="K7">
+        <v>4.67</v>
+      </c>
+      <c r="L7">
+        <v>50.97</v>
+      </c>
+      <c r="M7">
+        <v>2.224625797305277</v>
+      </c>
+      <c r="N7">
+        <v>48.74537420269472</v>
+      </c>
+      <c r="O7">
+        <v>12.18634355067368</v>
+      </c>
+      <c r="P7">
+        <v>36.55903065202104</v>
+      </c>
+      <c r="Q7">
+        <v>41.22903065202104</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1104390335035292</v>
+      </c>
+      <c r="T7">
+        <v>0.8259900045785007</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.034275</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>22.9117184839539</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1064132854186608</v>
+      </c>
+      <c r="C8">
+        <v>933.5710290668293</v>
+      </c>
+      <c r="D8">
+        <v>945.785710834145</v>
+      </c>
+      <c r="E8">
+        <v>45.3366523120527</v>
+      </c>
+      <c r="F8">
+        <v>58.41468176731578</v>
+      </c>
+      <c r="G8">
+        <v>46.2</v>
+      </c>
+      <c r="H8">
+        <v>960.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>55.64</v>
+      </c>
+      <c r="K8">
+        <v>4.67</v>
+      </c>
+      <c r="L8">
+        <v>50.97</v>
+      </c>
+      <c r="M8">
+        <v>2.669550956766332</v>
+      </c>
+      <c r="N8">
+        <v>48.30044904323367</v>
+      </c>
+      <c r="O8">
+        <v>12.07511226080842</v>
+      </c>
+      <c r="P8">
+        <v>36.22533678242525</v>
+      </c>
+      <c r="Q8">
+        <v>40.89533678242525</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1110178568283625</v>
+      </c>
+      <c r="T8">
+        <v>0.8326637724582086</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.034275</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>19.09309873662826</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1061957390089687</v>
+      </c>
+      <c r="C9">
+        <v>926.8881463108379</v>
+      </c>
+      <c r="D9">
+        <v>948.8386083727063</v>
+      </c>
+      <c r="E9">
+        <v>55.07243260660534</v>
+      </c>
+      <c r="F9">
+        <v>68.15046206186842</v>
+      </c>
+      <c r="G9">
+        <v>46.2</v>
+      </c>
+      <c r="H9">
+        <v>960.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>55.64</v>
+      </c>
+      <c r="K9">
+        <v>4.67</v>
+      </c>
+      <c r="L9">
+        <v>50.97</v>
+      </c>
+      <c r="M9">
+        <v>3.114476116227388</v>
+      </c>
+      <c r="N9">
+        <v>47.85552388377261</v>
+      </c>
+      <c r="O9">
+        <v>11.96388097094315</v>
+      </c>
+      <c r="P9">
+        <v>35.89164291282946</v>
+      </c>
+      <c r="Q9">
+        <v>40.56164291282946</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.111609127966633</v>
+      </c>
+      <c r="T9">
+        <v>0.8394810622278025</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.034275</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>16.36551320282422</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1059781925992767</v>
+      </c>
+      <c r="C10">
+        <v>920.2250362481261</v>
+      </c>
+      <c r="D10">
+        <v>951.9112786045471</v>
+      </c>
+      <c r="E10">
+        <v>64.80821290115796</v>
+      </c>
+      <c r="F10">
+        <v>77.88624235642105</v>
+      </c>
+      <c r="G10">
+        <v>46.2</v>
+      </c>
+      <c r="H10">
+        <v>960.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>55.64</v>
+      </c>
+      <c r="K10">
+        <v>4.67</v>
+      </c>
+      <c r="L10">
+        <v>50.97</v>
+      </c>
+      <c r="M10">
+        <v>3.559401275688443</v>
+      </c>
+      <c r="N10">
+        <v>47.41059872431155</v>
+      </c>
+      <c r="O10">
+        <v>11.85264968107789</v>
+      </c>
+      <c r="P10">
+        <v>35.55794904323366</v>
+      </c>
+      <c r="Q10">
+        <v>40.22794904323366</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1122132528253007</v>
+      </c>
+      <c r="T10">
+        <v>0.8464465539489094</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.034275</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>14.31982405247119</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1058686461895847</v>
+      </c>
+      <c r="C11">
+        <v>912.0440579190359</v>
+      </c>
+      <c r="D11">
+        <v>953.4660805700096</v>
+      </c>
+      <c r="E11">
+        <v>74.54399319571058</v>
+      </c>
+      <c r="F11">
+        <v>87.62202265097368</v>
+      </c>
+      <c r="G11">
+        <v>46.2</v>
+      </c>
+      <c r="H11">
+        <v>960.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>55.64</v>
+      </c>
+      <c r="K11">
+        <v>4.67</v>
+      </c>
+      <c r="L11">
+        <v>50.97</v>
+      </c>
+      <c r="M11">
+        <v>4.144521671391055</v>
+      </c>
+      <c r="N11">
+        <v>46.82547832860894</v>
+      </c>
+      <c r="O11">
+        <v>11.70636958215224</v>
+      </c>
+      <c r="P11">
+        <v>35.11910874645671</v>
+      </c>
+      <c r="Q11">
+        <v>39.78910874645671</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1128306551533897</v>
+      </c>
+      <c r="T11">
+        <v>0.8535651334001505</v>
+      </c>
+      <c r="U11">
+        <v>0.0473</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.035475</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>12.29816225882891</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1056630997798926</v>
+      </c>
+      <c r="C12">
+        <v>905.2393641321307</v>
+      </c>
+      <c r="D12">
+        <v>956.3971670776569</v>
+      </c>
+      <c r="E12">
+        <v>84.27977349026322</v>
+      </c>
+      <c r="F12">
+        <v>97.35780294552632</v>
+      </c>
+      <c r="G12">
+        <v>46.2</v>
+      </c>
+      <c r="H12">
+        <v>960.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>55.64</v>
+      </c>
+      <c r="K12">
+        <v>4.67</v>
+      </c>
+      <c r="L12">
+        <v>50.97</v>
+      </c>
+      <c r="M12">
+        <v>4.605024079323395</v>
+      </c>
+      <c r="N12">
+        <v>46.36497592067661</v>
+      </c>
+      <c r="O12">
+        <v>11.59124398016915</v>
+      </c>
+      <c r="P12">
+        <v>34.77373194050745</v>
+      </c>
+      <c r="Q12">
+        <v>39.44373194050745</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.113461777533214</v>
+      </c>
+      <c r="T12">
+        <v>0.8608419035058635</v>
+      </c>
+      <c r="U12">
+        <v>0.0473</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.035475</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>11.06834603294602</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1057710533702006</v>
+      </c>
+      <c r="C13">
+        <v>893.9619251245859</v>
+      </c>
+      <c r="D13">
+        <v>954.8555083646648</v>
+      </c>
+      <c r="E13">
+        <v>94.01555378481585</v>
+      </c>
+      <c r="F13">
+        <v>107.0935832400789</v>
+      </c>
+      <c r="G13">
+        <v>46.2</v>
+      </c>
+      <c r="H13">
+        <v>960.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>55.64</v>
+      </c>
+      <c r="K13">
+        <v>4.67</v>
+      </c>
+      <c r="L13">
+        <v>50.97</v>
+      </c>
+      <c r="M13">
+        <v>5.472482103568034</v>
+      </c>
+      <c r="N13">
+        <v>45.49751789643197</v>
+      </c>
+      <c r="O13">
+        <v>11.37437947410799</v>
+      </c>
+      <c r="P13">
+        <v>34.12313842232398</v>
+      </c>
+      <c r="Q13">
+        <v>38.79313842232398</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1141070824384276</v>
+      </c>
+      <c r="T13">
+        <v>0.8682821965353007</v>
+      </c>
+      <c r="U13">
+        <v>0.0511</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.038325</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>9.313872395629724</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1055940069605086</v>
+      </c>
+      <c r="C14">
+        <v>886.7571165028451</v>
+      </c>
+      <c r="D14">
+        <v>957.3864800374765</v>
+      </c>
+      <c r="E14">
+        <v>103.7513340793685</v>
+      </c>
+      <c r="F14">
+        <v>116.8293635346316</v>
+      </c>
+      <c r="G14">
+        <v>46.2</v>
+      </c>
+      <c r="H14">
+        <v>960.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>55.64</v>
+      </c>
+      <c r="K14">
+        <v>4.67</v>
+      </c>
+      <c r="L14">
+        <v>50.97</v>
+      </c>
+      <c r="M14">
+        <v>5.969980476619673</v>
+      </c>
+      <c r="N14">
+        <v>45.00001952338032</v>
+      </c>
+      <c r="O14">
+        <v>11.25000488084508</v>
+      </c>
+      <c r="P14">
+        <v>33.75001464253524</v>
+      </c>
+      <c r="Q14">
+        <v>38.42001464253524</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1147670533642143</v>
+      </c>
+      <c r="T14">
+        <v>0.8758915871335885</v>
+      </c>
+      <c r="U14">
+        <v>0.0511</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.038325</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>8.537716362660582</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1054169605508165</v>
+      </c>
+      <c r="C15">
+        <v>879.5657608949913</v>
+      </c>
+      <c r="D15">
+        <v>959.9309047241754</v>
+      </c>
+      <c r="E15">
+        <v>113.4871143739211</v>
+      </c>
+      <c r="F15">
+        <v>126.5651438291842</v>
+      </c>
+      <c r="G15">
+        <v>46.2</v>
+      </c>
+      <c r="H15">
+        <v>960.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>55.64</v>
+      </c>
+      <c r="K15">
+        <v>4.67</v>
+      </c>
+      <c r="L15">
+        <v>50.97</v>
+      </c>
+      <c r="M15">
+        <v>6.467478849671313</v>
+      </c>
+      <c r="N15">
+        <v>44.50252115032869</v>
+      </c>
+      <c r="O15">
+        <v>11.12563028758217</v>
+      </c>
+      <c r="P15">
+        <v>33.37689086274652</v>
+      </c>
+      <c r="Q15">
+        <v>38.04689086274652</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1154421960354213</v>
+      </c>
+      <c r="T15">
+        <v>0.8836759062513773</v>
+      </c>
+      <c r="U15">
+        <v>0.0511</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.038325</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>7.88096895014823</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1054394141411245</v>
+      </c>
+      <c r="C16">
+        <v>869.5065399529412</v>
+      </c>
+      <c r="D16">
+        <v>959.6074640766781</v>
+      </c>
+      <c r="E16">
+        <v>123.2228946684738</v>
+      </c>
+      <c r="F16">
+        <v>136.3009241237368</v>
+      </c>
+      <c r="G16">
+        <v>46.2</v>
+      </c>
+      <c r="H16">
+        <v>960.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>55.64</v>
+      </c>
+      <c r="K16">
+        <v>4.67</v>
+      </c>
+      <c r="L16">
+        <v>50.97</v>
+      </c>
+      <c r="M16">
+        <v>7.223948978558053</v>
+      </c>
+      <c r="N16">
+        <v>43.74605102144194</v>
+      </c>
+      <c r="O16">
+        <v>10.93651275536049</v>
+      </c>
+      <c r="P16">
+        <v>32.80953826608146</v>
+      </c>
+      <c r="Q16">
+        <v>37.47953826608146</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.116133039698982</v>
+      </c>
+      <c r="T16">
+        <v>0.8916412560463238</v>
+      </c>
+      <c r="U16">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>7.055697673293082</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1052766177314324</v>
+      </c>
+      <c r="C17">
+        <v>862.1207686569888</v>
+      </c>
+      <c r="D17">
+        <v>961.9574730752782</v>
+      </c>
+      <c r="E17">
+        <v>132.9586749630264</v>
+      </c>
+      <c r="F17">
+        <v>146.0367044182894</v>
+      </c>
+      <c r="G17">
+        <v>46.2</v>
+      </c>
+      <c r="H17">
+        <v>960.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>55.64</v>
+      </c>
+      <c r="K17">
+        <v>4.67</v>
+      </c>
+      <c r="L17">
+        <v>50.97</v>
+      </c>
+      <c r="M17">
+        <v>7.739945334169342</v>
+      </c>
+      <c r="N17">
+        <v>43.23005466583066</v>
+      </c>
+      <c r="O17">
+        <v>10.80751366645766</v>
+      </c>
+      <c r="P17">
+        <v>32.42254099937299</v>
+      </c>
+      <c r="Q17">
+        <v>37.09254099937299</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1168401385075676</v>
+      </c>
+      <c r="T17">
+        <v>0.8997940258364456</v>
+      </c>
+      <c r="U17">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>6.585317828406878</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1053538213217404</v>
+      </c>
+      <c r="C18">
+        <v>851.2691009622828</v>
+      </c>
+      <c r="D18">
+        <v>960.8415856751249</v>
+      </c>
+      <c r="E18">
+        <v>142.694455257579</v>
+      </c>
+      <c r="F18">
+        <v>155.7724847128421</v>
+      </c>
+      <c r="G18">
+        <v>46.2</v>
+      </c>
+      <c r="H18">
+        <v>960.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>55.64</v>
+      </c>
+      <c r="K18">
+        <v>4.67</v>
+      </c>
+      <c r="L18">
+        <v>50.97</v>
+      </c>
+      <c r="M18">
+        <v>8.567486659206315</v>
+      </c>
+      <c r="N18">
+        <v>42.40251334079368</v>
+      </c>
+      <c r="O18">
+        <v>10.60062833519842</v>
+      </c>
+      <c r="P18">
+        <v>31.80188500559526</v>
+      </c>
+      <c r="Q18">
+        <v>36.47188500559526</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1175640730020719</v>
+      </c>
+      <c r="T18">
+        <v>0.9081409091929989</v>
+      </c>
+      <c r="U18">
+        <v>0.055</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.04125</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.949235992708487</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1052060249120484</v>
+      </c>
+      <c r="C19">
+        <v>843.6718154328308</v>
+      </c>
+      <c r="D19">
+        <v>962.9800804402255</v>
+      </c>
+      <c r="E19">
+        <v>152.4302355521316</v>
+      </c>
+      <c r="F19">
+        <v>165.5082650073947</v>
+      </c>
+      <c r="G19">
+        <v>46.2</v>
+      </c>
+      <c r="H19">
+        <v>960.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>55.64</v>
+      </c>
+      <c r="K19">
+        <v>4.67</v>
+      </c>
+      <c r="L19">
+        <v>50.97</v>
+      </c>
+      <c r="M19">
+        <v>9.102954575406709</v>
+      </c>
+      <c r="N19">
+        <v>41.86704542459329</v>
+      </c>
+      <c r="O19">
+        <v>10.46676135614832</v>
+      </c>
+      <c r="P19">
+        <v>31.40028406844496</v>
+      </c>
+      <c r="Q19">
+        <v>36.07028406844496</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1183054517012631</v>
+      </c>
+      <c r="T19">
+        <v>0.9166889222689875</v>
+      </c>
+      <c r="U19">
+        <v>0.055</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.04125</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>5.59928093431387</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1050582285023564</v>
+      </c>
+      <c r="C20">
+        <v>836.0840702082007</v>
+      </c>
+      <c r="D20">
+        <v>965.1281155101481</v>
+      </c>
+      <c r="E20">
+        <v>162.1660158466843</v>
+      </c>
+      <c r="F20">
+        <v>175.2440453019474</v>
+      </c>
+      <c r="G20">
+        <v>46.2</v>
+      </c>
+      <c r="H20">
+        <v>960.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>55.64</v>
+      </c>
+      <c r="K20">
+        <v>4.67</v>
+      </c>
+      <c r="L20">
+        <v>50.97</v>
+      </c>
+      <c r="M20">
+        <v>9.638422491607104</v>
+      </c>
+      <c r="N20">
+        <v>41.3315775083929</v>
+      </c>
+      <c r="O20">
+        <v>10.33289437709822</v>
+      </c>
+      <c r="P20">
+        <v>30.99868313129467</v>
+      </c>
+      <c r="Q20">
+        <v>35.66868313129467</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1190649128077517</v>
+      </c>
+      <c r="T20">
+        <v>0.9254454234687801</v>
+      </c>
+      <c r="U20">
+        <v>0.055</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.04125</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>5.288209771296433</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1049104320926643</v>
+      </c>
+      <c r="C21">
+        <v>828.5059292732774</v>
+      </c>
+      <c r="D21">
+        <v>967.2857548697773</v>
+      </c>
+      <c r="E21">
+        <v>171.9017961412369</v>
+      </c>
+      <c r="F21">
+        <v>184.9798255965</v>
+      </c>
+      <c r="G21">
+        <v>46.2</v>
+      </c>
+      <c r="H21">
+        <v>960.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>55.64</v>
+      </c>
+      <c r="K21">
+        <v>4.67</v>
+      </c>
+      <c r="L21">
+        <v>50.97</v>
+      </c>
+      <c r="M21">
+        <v>10.1738904078075</v>
+      </c>
+      <c r="N21">
+        <v>40.7961095921925</v>
+      </c>
+      <c r="O21">
+        <v>10.19902739804813</v>
+      </c>
+      <c r="P21">
+        <v>30.59708219414438</v>
+      </c>
+      <c r="Q21">
+        <v>35.26708219414438</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1198431260403263</v>
+      </c>
+      <c r="T21">
+        <v>0.934418134574741</v>
+      </c>
+      <c r="U21">
+        <v>0.055</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.04125</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>5.0098829412282</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1047626356829723</v>
+      </c>
+      <c r="C22">
+        <v>820.9374571864062</v>
+      </c>
+      <c r="D22">
+        <v>969.4530630774588</v>
+      </c>
+      <c r="E22">
+        <v>181.6375764357896</v>
+      </c>
+      <c r="F22">
+        <v>194.7156058910526</v>
+      </c>
+      <c r="G22">
+        <v>46.2</v>
+      </c>
+      <c r="H22">
+        <v>960.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>55.64</v>
+      </c>
+      <c r="K22">
+        <v>4.67</v>
+      </c>
+      <c r="L22">
+        <v>50.97</v>
+      </c>
+      <c r="M22">
+        <v>10.70935832400789</v>
+      </c>
+      <c r="N22">
+        <v>40.2606416759921</v>
+      </c>
+      <c r="O22">
+        <v>10.06516041899803</v>
+      </c>
+      <c r="P22">
+        <v>30.19548125699408</v>
+      </c>
+      <c r="Q22">
+        <v>34.86548125699408</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1206407946037154</v>
+      </c>
+      <c r="T22">
+        <v>0.9436151634583505</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.04125</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>4.759388794166789</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1046148392732803</v>
+      </c>
+      <c r="C23">
+        <v>813.3787190858314</v>
+      </c>
+      <c r="D23">
+        <v>971.6301052714366</v>
+      </c>
+      <c r="E23">
+        <v>191.3733567303422</v>
+      </c>
+      <c r="F23">
+        <v>204.4513861856052</v>
+      </c>
+      <c r="G23">
+        <v>46.2</v>
+      </c>
+      <c r="H23">
+        <v>960.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>55.64</v>
+      </c>
+      <c r="K23">
+        <v>4.67</v>
+      </c>
+      <c r="L23">
+        <v>50.97</v>
+      </c>
+      <c r="M23">
+        <v>11.24482624020829</v>
+      </c>
+      <c r="N23">
+        <v>39.72517375979171</v>
+      </c>
+      <c r="O23">
+        <v>9.931293439947927</v>
+      </c>
+      <c r="P23">
+        <v>29.79388031984378</v>
+      </c>
+      <c r="Q23">
+        <v>34.46388031984378</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1214586573079497</v>
+      </c>
+      <c r="T23">
+        <v>0.9530450285162287</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.04125</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>4.532751232539799</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1050940428635882</v>
+      </c>
+      <c r="C24">
+        <v>796.6195530572776</v>
+      </c>
+      <c r="D24">
+        <v>964.6067195374354</v>
+      </c>
+      <c r="E24">
+        <v>201.1091370248948</v>
+      </c>
+      <c r="F24">
+        <v>214.1871664801579</v>
+      </c>
+      <c r="G24">
+        <v>46.2</v>
+      </c>
+      <c r="H24">
+        <v>960.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>55.64</v>
+      </c>
+      <c r="K24">
+        <v>4.67</v>
+      </c>
+      <c r="L24">
+        <v>50.97</v>
+      </c>
+      <c r="M24">
+        <v>12.59420538903328</v>
+      </c>
+      <c r="N24">
+        <v>38.37579461096671</v>
+      </c>
+      <c r="O24">
+        <v>9.593948652741679</v>
+      </c>
+      <c r="P24">
+        <v>28.78184595822503</v>
+      </c>
+      <c r="Q24">
+        <v>33.45184595822504</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1222974908507541</v>
+      </c>
+      <c r="T24">
+        <v>0.9627166849858474</v>
+      </c>
+      <c r="U24">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.0441</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>4.047099314767678</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1056992464538962</v>
+      </c>
+      <c r="C25">
+        <v>778.1574644581679</v>
+      </c>
+      <c r="D25">
+        <v>955.8804112328784</v>
+      </c>
+      <c r="E25">
+        <v>210.8449173194474</v>
+      </c>
+      <c r="F25">
+        <v>223.9229467747105</v>
+      </c>
+      <c r="G25">
+        <v>46.2</v>
+      </c>
+      <c r="H25">
+        <v>960.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>55.64</v>
+      </c>
+      <c r="K25">
+        <v>4.67</v>
+      </c>
+      <c r="L25">
+        <v>50.97</v>
+      </c>
+      <c r="M25">
+        <v>14.10714564680676</v>
+      </c>
+      <c r="N25">
+        <v>36.86285435319324</v>
+      </c>
+      <c r="O25">
+        <v>9.215713588298309</v>
+      </c>
+      <c r="P25">
+        <v>27.64714076489493</v>
+      </c>
+      <c r="Q25">
+        <v>32.31714076489493</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1231581122777873</v>
+      </c>
+      <c r="T25">
+        <v>0.9726395533118199</v>
+      </c>
+      <c r="U25">
+        <v>0.063</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.04725</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.613062576662159</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1068894500442042</v>
+      </c>
+      <c r="C26">
+        <v>751.7128945256342</v>
+      </c>
+      <c r="D26">
+        <v>939.1716215948973</v>
+      </c>
+      <c r="E26">
+        <v>220.5806976140001</v>
+      </c>
+      <c r="F26">
+        <v>233.6587270692631</v>
+      </c>
+      <c r="G26">
+        <v>46.2</v>
+      </c>
+      <c r="H26">
+        <v>960.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>55.64</v>
+      </c>
+      <c r="K26">
+        <v>4.67</v>
+      </c>
+      <c r="L26">
+        <v>50.97</v>
+      </c>
+      <c r="M26">
+        <v>16.37947676755535</v>
+      </c>
+      <c r="N26">
+        <v>34.59052323244465</v>
+      </c>
+      <c r="O26">
+        <v>8.647630808111163</v>
+      </c>
+      <c r="P26">
+        <v>25.94289242433349</v>
+      </c>
+      <c r="Q26">
+        <v>30.61289242433349</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1240413816371108</v>
+      </c>
+      <c r="T26">
+        <v>0.9828235497516339</v>
+      </c>
+      <c r="U26">
+        <v>0.0701</v>
+      </c>
+      <c r="V26">
+        <v>0.25</v>
+      </c>
+      <c r="W26">
+        <v>0.052575</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>3.111821013779998</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1108486536345121</v>
+      </c>
+      <c r="C27">
+        <v>690.3679380902422</v>
+      </c>
+      <c r="D27">
+        <v>887.562445454058</v>
+      </c>
+      <c r="E27">
+        <v>230.3164779085527</v>
+      </c>
+      <c r="F27">
+        <v>243.3945073638158</v>
+      </c>
+      <c r="G27">
+        <v>46.2</v>
+      </c>
+      <c r="H27">
+        <v>960.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>55.64</v>
+      </c>
+      <c r="K27">
+        <v>4.67</v>
+      </c>
+      <c r="L27">
+        <v>50.97</v>
+      </c>
+      <c r="M27">
+        <v>22.24625797305276</v>
+      </c>
+      <c r="N27">
+        <v>28.72374202694724</v>
+      </c>
+      <c r="O27">
+        <v>7.180935506736809</v>
+      </c>
+      <c r="P27">
+        <v>21.54280652021043</v>
+      </c>
+      <c r="Q27">
+        <v>26.21280652021043</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1249482048460162</v>
+      </c>
+      <c r="T27">
+        <v>0.9932791194298427</v>
+      </c>
+      <c r="U27">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V27">
+        <v>0.25</v>
+      </c>
+      <c r="W27">
+        <v>0.06855</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>2.291171848395391</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1109738572248201</v>
+      </c>
+      <c r="C28">
+        <v>679.0924589481245</v>
+      </c>
+      <c r="D28">
+        <v>886.0227466064929</v>
+      </c>
+      <c r="E28">
+        <v>240.0522582031053</v>
+      </c>
+      <c r="F28">
+        <v>253.1302876583684</v>
+      </c>
+      <c r="G28">
+        <v>46.2</v>
+      </c>
+      <c r="H28">
+        <v>960.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>55.64</v>
+      </c>
+      <c r="K28">
+        <v>4.67</v>
+      </c>
+      <c r="L28">
+        <v>50.97</v>
+      </c>
+      <c r="M28">
+        <v>23.13610829197487</v>
+      </c>
+      <c r="N28">
+        <v>27.83389170802512</v>
+      </c>
+      <c r="O28">
+        <v>6.958472927006281</v>
+      </c>
+      <c r="P28">
+        <v>20.87541878101884</v>
+      </c>
+      <c r="Q28">
+        <v>25.54541878101885</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1258795367902975</v>
+      </c>
+      <c r="T28">
+        <v>1.004017272072327</v>
+      </c>
+      <c r="U28">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.25</v>
+      </c>
+      <c r="W28">
+        <v>0.06855</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>2.203049854226337</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1110990608151281</v>
+      </c>
+      <c r="C29">
+        <v>667.8223125398363</v>
+      </c>
+      <c r="D29">
+        <v>884.4883804927572</v>
+      </c>
+      <c r="E29">
+        <v>249.7880384976579</v>
+      </c>
+      <c r="F29">
+        <v>262.866067952921</v>
+      </c>
+      <c r="G29">
+        <v>46.2</v>
+      </c>
+      <c r="H29">
+        <v>960.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>55.64</v>
+      </c>
+      <c r="K29">
+        <v>4.67</v>
+      </c>
+      <c r="L29">
+        <v>50.97</v>
+      </c>
+      <c r="M29">
+        <v>24.02595861089698</v>
+      </c>
+      <c r="N29">
+        <v>26.94404138910302</v>
+      </c>
+      <c r="O29">
+        <v>6.736010347275754</v>
+      </c>
+      <c r="P29">
+        <v>20.20803104182726</v>
+      </c>
+      <c r="Q29">
+        <v>24.87803104182726</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1268363846782576</v>
+      </c>
+      <c r="T29">
+        <v>1.01504962067762</v>
+      </c>
+      <c r="U29">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0.25</v>
+      </c>
+      <c r="W29">
+        <v>0.06855</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>2.121455415180917</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.111224264405436</v>
+      </c>
+      <c r="C30">
+        <v>656.5574712084542</v>
+      </c>
+      <c r="D30">
+        <v>882.9593194559279</v>
+      </c>
+      <c r="E30">
+        <v>259.5238187922106</v>
+      </c>
+      <c r="F30">
+        <v>272.6018482474737</v>
+      </c>
+      <c r="G30">
+        <v>46.2</v>
+      </c>
+      <c r="H30">
+        <v>960.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>55.64</v>
+      </c>
+      <c r="K30">
+        <v>4.67</v>
+      </c>
+      <c r="L30">
+        <v>50.97</v>
+      </c>
+      <c r="M30">
+        <v>24.9158089298191</v>
+      </c>
+      <c r="N30">
+        <v>26.0541910701809</v>
+      </c>
+      <c r="O30">
+        <v>6.513547767545225</v>
+      </c>
+      <c r="P30">
+        <v>19.54064330263567</v>
+      </c>
+      <c r="Q30">
+        <v>24.21064330263567</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1278198116742167</v>
+      </c>
+      <c r="T30">
+        <v>1.026388423410837</v>
+      </c>
+      <c r="U30">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V30">
+        <v>0.25</v>
+      </c>
+      <c r="W30">
+        <v>0.06855</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>2.045689150353027</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.115938717995744</v>
+      </c>
+      <c r="C31">
+        <v>592.8582489244388</v>
+      </c>
+      <c r="D31">
+        <v>828.995877466465</v>
+      </c>
+      <c r="E31">
+        <v>269.2595990867632</v>
+      </c>
+      <c r="F31">
+        <v>282.3376285420263</v>
+      </c>
+      <c r="G31">
+        <v>46.2</v>
+      </c>
+      <c r="H31">
+        <v>960.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>55.64</v>
+      </c>
+      <c r="K31">
+        <v>4.67</v>
+      </c>
+      <c r="L31">
+        <v>50.97</v>
+      </c>
+      <c r="M31">
+        <v>31.76298321097796</v>
+      </c>
+      <c r="N31">
+        <v>19.20701678902204</v>
+      </c>
+      <c r="O31">
+        <v>4.80175419725551</v>
+      </c>
+      <c r="P31">
+        <v>14.40526259176653</v>
+      </c>
+      <c r="Q31">
+        <v>19.07526259176653</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1288309408390761</v>
+      </c>
+      <c r="T31">
+        <v>1.038046629037948</v>
+      </c>
+      <c r="U31">
+        <v>0.1125</v>
+      </c>
+      <c r="V31">
+        <v>0.25</v>
+      </c>
+      <c r="W31">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>1.604698137496849</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.116222171586052</v>
+      </c>
+      <c r="C32">
+        <v>580.0873967247122</v>
+      </c>
+      <c r="D32">
+        <v>825.9608055612911</v>
+      </c>
+      <c r="E32">
+        <v>278.9953793813158</v>
+      </c>
+      <c r="F32">
+        <v>292.0734088365789</v>
+      </c>
+      <c r="G32">
+        <v>46.2</v>
+      </c>
+      <c r="H32">
+        <v>960.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>55.64</v>
+      </c>
+      <c r="K32">
+        <v>4.67</v>
+      </c>
+      <c r="L32">
+        <v>50.97</v>
+      </c>
+      <c r="M32">
+        <v>32.85825849411513</v>
+      </c>
+      <c r="N32">
+        <v>18.11174150588487</v>
+      </c>
+      <c r="O32">
+        <v>4.527935376471218</v>
+      </c>
+      <c r="P32">
+        <v>13.58380612941365</v>
+      </c>
+      <c r="Q32">
+        <v>18.25380612941365</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1298709594086457</v>
+      </c>
+      <c r="T32">
+        <v>1.050037926254405</v>
+      </c>
+      <c r="U32">
+        <v>0.1125</v>
+      </c>
+      <c r="V32">
+        <v>0.25</v>
+      </c>
+      <c r="W32">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>1.551208199580287</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1165056251763599</v>
+      </c>
+      <c r="C33">
+        <v>567.3386871183029</v>
+      </c>
+      <c r="D33">
+        <v>822.9478762494343</v>
+      </c>
+      <c r="E33">
+        <v>288.7311596758684</v>
+      </c>
+      <c r="F33">
+        <v>301.8091891311315</v>
+      </c>
+      <c r="G33">
+        <v>46.2</v>
+      </c>
+      <c r="H33">
+        <v>960.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>55.64</v>
+      </c>
+      <c r="K33">
+        <v>4.67</v>
+      </c>
+      <c r="L33">
+        <v>50.97</v>
+      </c>
+      <c r="M33">
+        <v>33.9535337772523</v>
+      </c>
+      <c r="N33">
+        <v>17.0164662227477</v>
+      </c>
+      <c r="O33">
+        <v>4.254116555686926</v>
+      </c>
+      <c r="P33">
+        <v>12.76234966706078</v>
+      </c>
+      <c r="Q33">
+        <v>17.43234966706078</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1309411234439999</v>
+      </c>
+      <c r="T33">
+        <v>1.062376797303223</v>
+      </c>
+      <c r="U33">
+        <v>0.1125</v>
+      </c>
+      <c r="V33">
+        <v>0.25</v>
+      </c>
+      <c r="W33">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>1.501169225400278</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1405381055182878</v>
+      </c>
+      <c r="C34">
+        <v>363.2069274840255</v>
+      </c>
+      <c r="D34">
+        <v>628.5518969097096</v>
+      </c>
+      <c r="E34">
+        <v>298.4669399704211</v>
+      </c>
+      <c r="F34">
+        <v>311.5449694256842</v>
+      </c>
+      <c r="G34">
+        <v>46.2</v>
+      </c>
+      <c r="H34">
+        <v>960.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>55.64</v>
+      </c>
+      <c r="K34">
+        <v>4.67</v>
+      </c>
+      <c r="L34">
+        <v>50.97</v>
+      </c>
+      <c r="M34">
+        <v>61.24974098908951</v>
+      </c>
+      <c r="N34">
+        <v>-10.27974098908951</v>
+      </c>
+      <c r="O34">
+        <v>-2.569935247272378</v>
+      </c>
+      <c r="P34">
+        <v>-7.709805741817133</v>
+      </c>
+      <c r="Q34">
+        <v>-3.039805741817133</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1334035657385977</v>
+      </c>
+      <c r="T34">
+        <v>1.090768480198958</v>
+      </c>
+      <c r="U34">
+        <v>0.1966</v>
+      </c>
+      <c r="V34">
+        <v>0.2080416960827612</v>
+      </c>
+      <c r="W34">
+        <v>0.1556990025501292</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.8321667843310447</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1421161055182878</v>
+      </c>
+      <c r="C35">
+        <v>343.8709508953146</v>
+      </c>
+      <c r="D35">
+        <v>618.9517006155514</v>
+      </c>
+      <c r="E35">
+        <v>308.2027202649737</v>
+      </c>
+      <c r="F35">
+        <v>321.2807497202368</v>
+      </c>
+      <c r="G35">
+        <v>46.2</v>
+      </c>
+      <c r="H35">
+        <v>960.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>55.64</v>
+      </c>
+      <c r="K35">
+        <v>4.67</v>
+      </c>
+      <c r="L35">
+        <v>50.97</v>
+      </c>
+      <c r="M35">
+        <v>63.16379539499856</v>
+      </c>
+      <c r="N35">
+        <v>-12.19379539499856</v>
+      </c>
+      <c r="O35">
+        <v>-3.04844884874964</v>
+      </c>
+      <c r="P35">
+        <v>-9.14534654624892</v>
+      </c>
+      <c r="Q35">
+        <v>-4.47534654624892</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1348155592570843</v>
+      </c>
+      <c r="T35">
+        <v>1.107048606769092</v>
+      </c>
+      <c r="U35">
+        <v>0.1966</v>
+      </c>
+      <c r="V35">
+        <v>0.2017374022620714</v>
+      </c>
+      <c r="W35">
+        <v>0.1569384267152767</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.8069496090482857</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1499112168082903</v>
+      </c>
+      <c r="C36">
+        <v>290.7120354031771</v>
+      </c>
+      <c r="D36">
+        <v>575.5285654179665</v>
+      </c>
+      <c r="E36">
+        <v>317.9385005595263</v>
+      </c>
+      <c r="F36">
+        <v>331.0165300147895</v>
+      </c>
+      <c r="G36">
+        <v>46.2</v>
+      </c>
+      <c r="H36">
+        <v>960.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>55.64</v>
+      </c>
+      <c r="K36">
+        <v>4.67</v>
+      </c>
+      <c r="L36">
+        <v>50.97</v>
+      </c>
+      <c r="M36">
+        <v>70.77133411716198</v>
+      </c>
+      <c r="N36">
+        <v>-19.80133411716199</v>
+      </c>
+      <c r="O36">
+        <v>-4.950333529290496</v>
+      </c>
+      <c r="P36">
+        <v>-14.85100058787149</v>
+      </c>
+      <c r="Q36">
+        <v>-10.18100058787149</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1368295999882561</v>
+      </c>
+      <c r="T36">
+        <v>1.130270270035667</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.1800517138606541</v>
+      </c>
+      <c r="W36">
+        <v>0.1753049435765922</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.7202068554426165</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1516612168082903</v>
+      </c>
+      <c r="C37">
+        <v>272.0522419005066</v>
+      </c>
+      <c r="D37">
+        <v>566.6045522098486</v>
+      </c>
+      <c r="E37">
+        <v>327.674280854079</v>
+      </c>
+      <c r="F37">
+        <v>340.7523103093421</v>
+      </c>
+      <c r="G37">
+        <v>46.2</v>
+      </c>
+      <c r="H37">
+        <v>960.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>55.64</v>
+      </c>
+      <c r="K37">
+        <v>4.67</v>
+      </c>
+      <c r="L37">
+        <v>50.97</v>
+      </c>
+      <c r="M37">
+        <v>72.85284394413733</v>
+      </c>
+      <c r="N37">
+        <v>-21.88284394413733</v>
+      </c>
+      <c r="O37">
+        <v>-5.470710986034334</v>
+      </c>
+      <c r="P37">
+        <v>-16.412132958103</v>
+      </c>
+      <c r="Q37">
+        <v>-11.742132958103</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1383377476803831</v>
+      </c>
+      <c r="T37">
+        <v>1.147659043420831</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.1749073791789212</v>
+      </c>
+      <c r="W37">
+        <v>0.1764048023315467</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.6996295167156847</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1534112168082903</v>
+      </c>
+      <c r="C38">
+        <v>253.6649701203884</v>
+      </c>
+      <c r="D38">
+        <v>557.9530607242831</v>
+      </c>
+      <c r="E38">
+        <v>337.4100611486316</v>
+      </c>
+      <c r="F38">
+        <v>350.4880906038947</v>
+      </c>
+      <c r="G38">
+        <v>46.2</v>
+      </c>
+      <c r="H38">
+        <v>960.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>55.64</v>
+      </c>
+      <c r="K38">
+        <v>4.67</v>
+      </c>
+      <c r="L38">
+        <v>50.97</v>
+      </c>
+      <c r="M38">
+        <v>74.93435377111268</v>
+      </c>
+      <c r="N38">
+        <v>-23.96435377111268</v>
+      </c>
+      <c r="O38">
+        <v>-5.991088442778171</v>
+      </c>
+      <c r="P38">
+        <v>-17.97326532833451</v>
+      </c>
+      <c r="Q38">
+        <v>-13.30326532833451</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1398930249878891</v>
+      </c>
+      <c r="T38">
+        <v>1.165591215974282</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1700488408683956</v>
+      </c>
+      <c r="W38">
+        <v>0.177443557822337</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.6801953634735824</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1551612168082903</v>
+      </c>
+      <c r="C39">
+        <v>235.5379243935039</v>
+      </c>
+      <c r="D39">
+        <v>549.5617952919512</v>
+      </c>
+      <c r="E39">
+        <v>347.1458414431842</v>
+      </c>
+      <c r="F39">
+        <v>360.2238708984473</v>
+      </c>
+      <c r="G39">
+        <v>46.2</v>
+      </c>
+      <c r="H39">
+        <v>960.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>55.64</v>
+      </c>
+      <c r="K39">
+        <v>4.67</v>
+      </c>
+      <c r="L39">
+        <v>50.97</v>
+      </c>
+      <c r="M39">
+        <v>77.01586359808803</v>
+      </c>
+      <c r="N39">
+        <v>-26.04586359808803</v>
+      </c>
+      <c r="O39">
+        <v>-6.511465899522008</v>
+      </c>
+      <c r="P39">
+        <v>-19.53439769856602</v>
+      </c>
+      <c r="Q39">
+        <v>-14.86439769856602</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.141497676178173</v>
+      </c>
+      <c r="T39">
+        <v>1.18409266384689</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.1654529262503308</v>
+      </c>
+      <c r="W39">
+        <v>0.1784261643676793</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.6618117050013235</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1569112168082903</v>
+      </c>
+      <c r="C40">
+        <v>217.6595377678189</v>
+      </c>
+      <c r="D40">
+        <v>541.4191889608188</v>
+      </c>
+      <c r="E40">
+        <v>356.8816217377369</v>
+      </c>
+      <c r="F40">
+        <v>369.959651193</v>
+      </c>
+      <c r="G40">
+        <v>46.2</v>
+      </c>
+      <c r="H40">
+        <v>960.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>55.64</v>
+      </c>
+      <c r="K40">
+        <v>4.67</v>
+      </c>
+      <c r="L40">
+        <v>50.97</v>
+      </c>
+      <c r="M40">
+        <v>79.09737342506338</v>
+      </c>
+      <c r="N40">
+        <v>-28.12737342506338</v>
+      </c>
+      <c r="O40">
+        <v>-7.031843356265846</v>
+      </c>
+      <c r="P40">
+        <v>-21.09553006879754</v>
+      </c>
+      <c r="Q40">
+        <v>-16.42553006879753</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.143154090310079</v>
+      </c>
+      <c r="T40">
+        <v>1.203190932618614</v>
+      </c>
+      <c r="U40">
+        <v>0.2138</v>
+      </c>
+      <c r="V40">
+        <v>0.1610989018753222</v>
+      </c>
+      <c r="W40">
+        <v>0.1793570547790561</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.6443956075012887</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1586612168082903</v>
+      </c>
+      <c r="C41">
+        <v>200.0189188114258</v>
+      </c>
+      <c r="D41">
+        <v>533.5143502989783</v>
+      </c>
+      <c r="E41">
+        <v>366.6174020322895</v>
+      </c>
+      <c r="F41">
+        <v>379.6954314875526</v>
+      </c>
+      <c r="G41">
+        <v>46.2</v>
+      </c>
+      <c r="H41">
+        <v>960.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>55.64</v>
+      </c>
+      <c r="K41">
+        <v>4.67</v>
+      </c>
+      <c r="L41">
+        <v>50.97</v>
+      </c>
+      <c r="M41">
+        <v>81.17888325203874</v>
+      </c>
+      <c r="N41">
+        <v>-30.20888325203875</v>
+      </c>
+      <c r="O41">
+        <v>-7.552220813009686</v>
+      </c>
+      <c r="P41">
+        <v>-22.65666243902906</v>
+      </c>
+      <c r="Q41">
+        <v>-17.98666243902906</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1448648131020475</v>
+      </c>
+      <c r="T41">
+        <v>1.222915374136951</v>
+      </c>
+      <c r="U41">
+        <v>0.2138</v>
+      </c>
+      <c r="V41">
+        <v>0.1569681608015959</v>
+      </c>
+      <c r="W41">
+        <v>0.1802402072206188</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.6278726432063837</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1604112168082903</v>
+      </c>
+      <c r="C42">
+        <v>182.6058030084632</v>
+      </c>
+      <c r="D42">
+        <v>525.8370147905684</v>
+      </c>
+      <c r="E42">
+        <v>376.3531823268422</v>
+      </c>
+      <c r="F42">
+        <v>389.4312117821053</v>
+      </c>
+      <c r="G42">
+        <v>46.2</v>
+      </c>
+      <c r="H42">
+        <v>960.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>55.64</v>
+      </c>
+      <c r="K42">
+        <v>4.67</v>
+      </c>
+      <c r="L42">
+        <v>50.97</v>
+      </c>
+      <c r="M42">
+        <v>83.26039307901411</v>
+      </c>
+      <c r="N42">
+        <v>-32.29039307901411</v>
+      </c>
+      <c r="O42">
+        <v>-8.072598269753527</v>
+      </c>
+      <c r="P42">
+        <v>-24.21779480926058</v>
+      </c>
+      <c r="Q42">
+        <v>-19.54779480926058</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1466325599870817</v>
+      </c>
+      <c r="T42">
+        <v>1.243297297039234</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.153043956781556</v>
+      </c>
+      <c r="W42">
+        <v>0.1810792020401033</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.6121758271262241</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1621612168082903</v>
+      </c>
+      <c r="C43">
+        <v>165.4105082920194</v>
+      </c>
+      <c r="D43">
+        <v>518.3775003686773</v>
+      </c>
+      <c r="E43">
+        <v>386.0889626213948</v>
+      </c>
+      <c r="F43">
+        <v>399.1669920766579</v>
+      </c>
+      <c r="G43">
+        <v>46.2</v>
+      </c>
+      <c r="H43">
+        <v>960.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>55.64</v>
+      </c>
+      <c r="K43">
+        <v>4.67</v>
+      </c>
+      <c r="L43">
+        <v>50.97</v>
+      </c>
+      <c r="M43">
+        <v>85.34190290598946</v>
+      </c>
+      <c r="N43">
+        <v>-34.37190290598946</v>
+      </c>
+      <c r="O43">
+        <v>-8.592975726497365</v>
+      </c>
+      <c r="P43">
+        <v>-25.77892717949209</v>
+      </c>
+      <c r="Q43">
+        <v>-21.10892717949209</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1484602304953373</v>
+      </c>
+      <c r="T43">
+        <v>1.264370132582272</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.1493111773478595</v>
+      </c>
+      <c r="W43">
+        <v>0.1818772702830276</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.5972447093914381</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1639112168082903</v>
+      </c>
+      <c r="C44">
+        <v>148.4238943089475</v>
+      </c>
+      <c r="D44">
+        <v>511.1266666801579</v>
+      </c>
+      <c r="E44">
+        <v>395.8247429159474</v>
+      </c>
+      <c r="F44">
+        <v>408.9027723712105</v>
+      </c>
+      <c r="G44">
+        <v>46.2</v>
+      </c>
+      <c r="H44">
+        <v>960.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>55.64</v>
+      </c>
+      <c r="K44">
+        <v>4.67</v>
+      </c>
+      <c r="L44">
+        <v>50.97</v>
+      </c>
+      <c r="M44">
+        <v>87.42341273296479</v>
+      </c>
+      <c r="N44">
+        <v>-36.45341273296479</v>
+      </c>
+      <c r="O44">
+        <v>-9.113353183241198</v>
+      </c>
+      <c r="P44">
+        <v>-27.34005954972359</v>
+      </c>
+      <c r="Q44">
+        <v>-22.6700595497236</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1503509241245672</v>
+      </c>
+      <c r="T44">
+        <v>1.286169617626794</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.1457561493157677</v>
+      </c>
+      <c r="W44">
+        <v>0.1826373352762889</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.5830245972630707</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1656612168082903</v>
+      </c>
+      <c r="C45">
+        <v>131.6373250562377</v>
+      </c>
+      <c r="D45">
+        <v>504.0758777220008</v>
+      </c>
+      <c r="E45">
+        <v>405.5605232105</v>
+      </c>
+      <c r="F45">
+        <v>418.6385526657631</v>
+      </c>
+      <c r="G45">
+        <v>46.2</v>
+      </c>
+      <c r="H45">
+        <v>960.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>55.64</v>
+      </c>
+      <c r="K45">
+        <v>4.67</v>
+      </c>
+      <c r="L45">
+        <v>50.97</v>
+      </c>
+      <c r="M45">
+        <v>89.50492255994014</v>
+      </c>
+      <c r="N45">
+        <v>-38.53492255994014</v>
+      </c>
+      <c r="O45">
+        <v>-9.633730639985036</v>
+      </c>
+      <c r="P45">
+        <v>-28.90119191995511</v>
+      </c>
+      <c r="Q45">
+        <v>-24.23119191995511</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1523079578811386</v>
+      </c>
+      <c r="T45">
+        <v>1.308733996883404</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.1423664714247033</v>
+      </c>
+      <c r="W45">
+        <v>0.1833620484093984</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.5694658856988132</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1674112168082904</v>
+      </c>
+      <c r="C46">
+        <v>115.0426345678064</v>
+      </c>
+      <c r="D46">
+        <v>497.2169675281222</v>
+      </c>
+      <c r="E46">
+        <v>415.2963035050527</v>
+      </c>
+      <c r="F46">
+        <v>428.3743329603158</v>
+      </c>
+      <c r="G46">
+        <v>46.2</v>
+      </c>
+      <c r="H46">
+        <v>960.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>55.64</v>
+      </c>
+      <c r="K46">
+        <v>4.67</v>
+      </c>
+      <c r="L46">
+        <v>50.97</v>
+      </c>
+      <c r="M46">
+        <v>91.5864323869155</v>
+      </c>
+      <c r="N46">
+        <v>-40.61643238691551</v>
+      </c>
+      <c r="O46">
+        <v>-10.15410809672888</v>
+      </c>
+      <c r="P46">
+        <v>-30.46232429018663</v>
+      </c>
+      <c r="Q46">
+        <v>-25.79232429018663</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1543348857004447</v>
+      </c>
+      <c r="T46">
+        <v>1.332104246827751</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.1391308698014146</v>
+      </c>
+      <c r="W46">
+        <v>0.1840538200364576</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.5565234792056583</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1691612168082903</v>
+      </c>
+      <c r="C47">
+        <v>98.63209536505934</v>
+      </c>
+      <c r="D47">
+        <v>490.5422086199277</v>
+      </c>
+      <c r="E47">
+        <v>425.0320837996053</v>
+      </c>
+      <c r="F47">
+        <v>438.1101132548684</v>
+      </c>
+      <c r="G47">
+        <v>46.2</v>
+      </c>
+      <c r="H47">
+        <v>960.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>55.64</v>
+      </c>
+      <c r="K47">
+        <v>4.67</v>
+      </c>
+      <c r="L47">
+        <v>50.97</v>
+      </c>
+      <c r="M47">
+        <v>93.66794221389085</v>
+      </c>
+      <c r="N47">
+        <v>-42.69794221389085</v>
+      </c>
+      <c r="O47">
+        <v>-10.67448555347271</v>
+      </c>
+      <c r="P47">
+        <v>-32.02345666041814</v>
+      </c>
+      <c r="Q47">
+        <v>-27.35345666041814</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1564355199859073</v>
+      </c>
+      <c r="T47">
+        <v>1.356324324042801</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.1360390726947165</v>
+      </c>
+      <c r="W47">
+        <v>0.1847148462578696</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.544156290778866</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1709112168082903</v>
+      </c>
+      <c r="C48">
+        <v>82.39838941495407</v>
+      </c>
+      <c r="D48">
+        <v>484.0442829643751</v>
+      </c>
+      <c r="E48">
+        <v>434.7678640941579</v>
+      </c>
+      <c r="F48">
+        <v>447.845893549421</v>
+      </c>
+      <c r="G48">
+        <v>46.2</v>
+      </c>
+      <c r="H48">
+        <v>960.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>55.64</v>
+      </c>
+      <c r="K48">
+        <v>4.67</v>
+      </c>
+      <c r="L48">
+        <v>50.97</v>
+      </c>
+      <c r="M48">
+        <v>95.74945204086622</v>
+      </c>
+      <c r="N48">
+        <v>-44.77945204086622</v>
+      </c>
+      <c r="O48">
+        <v>-11.19486301021655</v>
+      </c>
+      <c r="P48">
+        <v>-33.58458903064967</v>
+      </c>
+      <c r="Q48">
+        <v>-28.91458903064967</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1586139555412018</v>
+      </c>
+      <c r="T48">
+        <v>1.381441441154704</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1330817015491791</v>
+      </c>
+      <c r="W48">
+        <v>0.1853471322087855</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.5323268061967166</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1726612168082903</v>
+      </c>
+      <c r="C49">
+        <v>66.33458136609835</v>
+      </c>
+      <c r="D49">
+        <v>477.7162552100719</v>
+      </c>
+      <c r="E49">
+        <v>444.5036443887105</v>
+      </c>
+      <c r="F49">
+        <v>457.5816738439736</v>
+      </c>
+      <c r="G49">
+        <v>46.2</v>
+      </c>
+      <c r="H49">
+        <v>960.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>55.64</v>
+      </c>
+      <c r="K49">
+        <v>4.67</v>
+      </c>
+      <c r="L49">
+        <v>50.97</v>
+      </c>
+      <c r="M49">
+        <v>97.83096186784157</v>
+      </c>
+      <c r="N49">
+        <v>-46.86096186784157</v>
+      </c>
+      <c r="O49">
+        <v>-11.71524046696039</v>
+      </c>
+      <c r="P49">
+        <v>-35.14572140088117</v>
+      </c>
+      <c r="Q49">
+        <v>-30.47572140088117</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1608745962117906</v>
+      </c>
+      <c r="T49">
+        <v>1.40750637400668</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.130250175984303</v>
+      </c>
+      <c r="W49">
+        <v>0.185952512374556</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.521000703937212</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1744112168082903</v>
+      </c>
+      <c r="C50">
+        <v>50.43409385710152</v>
+      </c>
+      <c r="D50">
+        <v>471.5515479956278</v>
+      </c>
+      <c r="E50">
+        <v>454.2394246832632</v>
+      </c>
+      <c r="F50">
+        <v>467.3174541385263</v>
+      </c>
+      <c r="G50">
+        <v>46.2</v>
+      </c>
+      <c r="H50">
+        <v>960.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>55.64</v>
+      </c>
+      <c r="K50">
+        <v>4.67</v>
+      </c>
+      <c r="L50">
+        <v>50.97</v>
+      </c>
+      <c r="M50">
+        <v>99.91247169481692</v>
+      </c>
+      <c r="N50">
+        <v>-48.94247169481692</v>
+      </c>
+      <c r="O50">
+        <v>-12.23561792370423</v>
+      </c>
+      <c r="P50">
+        <v>-36.70685377111269</v>
+      </c>
+      <c r="Q50">
+        <v>-32.03685377111269</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1632221846004788</v>
+      </c>
+      <c r="T50">
+        <v>1.434573804276039</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.1275366306512967</v>
+      </c>
+      <c r="W50">
+        <v>0.1865326683667528</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.5101465226051867</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1888529073322187</v>
+      </c>
+      <c r="C51">
+        <v>-4.685688942346417</v>
+      </c>
+      <c r="D51">
+        <v>426.1675454907325</v>
+      </c>
+      <c r="E51">
+        <v>463.9752049778158</v>
+      </c>
+      <c r="F51">
+        <v>477.0532344330789</v>
+      </c>
+      <c r="G51">
+        <v>46.2</v>
+      </c>
+      <c r="H51">
+        <v>960.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>55.64</v>
+      </c>
+      <c r="K51">
+        <v>4.67</v>
+      </c>
+      <c r="L51">
+        <v>50.97</v>
+      </c>
+      <c r="M51">
+        <v>113.9203123826192</v>
+      </c>
+      <c r="N51">
+        <v>-62.95031238261924</v>
+      </c>
+      <c r="O51">
+        <v>-15.73757809565481</v>
+      </c>
+      <c r="P51">
+        <v>-47.21273428696443</v>
+      </c>
+      <c r="Q51">
+        <v>-42.54273428696443</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1665278951297596</v>
+      </c>
+      <c r="T51">
+        <v>1.472688275140324</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.1118545036744836</v>
+      </c>
+      <c r="W51">
+        <v>0.2120891445225333</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.4474180146979343</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1908529073322187</v>
+      </c>
+      <c r="C52">
+        <v>-20.02698580304536</v>
+      </c>
+      <c r="D52">
+        <v>420.5620289245862</v>
+      </c>
+      <c r="E52">
+        <v>473.7109852723684</v>
+      </c>
+      <c r="F52">
+        <v>486.7890147276315</v>
+      </c>
+      <c r="G52">
+        <v>46.2</v>
+      </c>
+      <c r="H52">
+        <v>960.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>55.64</v>
+      </c>
+      <c r="K52">
+        <v>4.67</v>
+      </c>
+      <c r="L52">
+        <v>50.97</v>
+      </c>
+      <c r="M52">
+        <v>116.2452167169584</v>
+      </c>
+      <c r="N52">
+        <v>-65.27521671695841</v>
+      </c>
+      <c r="O52">
+        <v>-16.3188041792396</v>
+      </c>
+      <c r="P52">
+        <v>-48.9564125377188</v>
+      </c>
+      <c r="Q52">
+        <v>-44.2864125377188</v>
+      </c>
+      <c r="R52">
         <v>1</v>
       </c>
-      <c r="AJ3">
-        <v>0.01881787819757204</v>
-      </c>
-      <c r="AK3">
-        <v>1</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>5.417268321709536</v>
+      <c r="S52">
+        <v>0.1690824530323548</v>
+      </c>
+      <c r="T52">
+        <v>1.502142040643131</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.1096174136009939</v>
+      </c>
+      <c r="W52">
+        <v>0.2126233616320827</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.4384696544039756</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1928529073322187</v>
+      </c>
+      <c r="C53">
+        <v>-35.22273483441171</v>
+      </c>
+      <c r="D53">
+        <v>415.1020601877725</v>
+      </c>
+      <c r="E53">
+        <v>483.446765566921</v>
+      </c>
+      <c r="F53">
+        <v>496.5247950221842</v>
+      </c>
+      <c r="G53">
+        <v>46.2</v>
+      </c>
+      <c r="H53">
+        <v>960.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>55.64</v>
+      </c>
+      <c r="K53">
+        <v>4.67</v>
+      </c>
+      <c r="L53">
+        <v>50.97</v>
+      </c>
+      <c r="M53">
+        <v>118.5701210512976</v>
+      </c>
+      <c r="N53">
+        <v>-67.60012105129758</v>
+      </c>
+      <c r="O53">
+        <v>-16.90003026282439</v>
+      </c>
+      <c r="P53">
+        <v>-50.70009078847318</v>
+      </c>
+      <c r="Q53">
+        <v>-46.03009078847318</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1717412786044437</v>
+      </c>
+      <c r="T53">
+        <v>1.532798000656256</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.107468052549994</v>
+      </c>
+      <c r="W53">
+        <v>0.2131366290510614</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.429872210199976</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1948529073322187</v>
+      </c>
+      <c r="C54">
+        <v>-50.27853213196789</v>
+      </c>
+      <c r="D54">
+        <v>409.7820431847689</v>
+      </c>
+      <c r="E54">
+        <v>493.1825458614737</v>
+      </c>
+      <c r="F54">
+        <v>506.2605753167368</v>
+      </c>
+      <c r="G54">
+        <v>46.2</v>
+      </c>
+      <c r="H54">
+        <v>960.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>55.64</v>
+      </c>
+      <c r="K54">
+        <v>4.67</v>
+      </c>
+      <c r="L54">
+        <v>50.97</v>
+      </c>
+      <c r="M54">
+        <v>120.8950253856367</v>
+      </c>
+      <c r="N54">
+        <v>-69.92502538563674</v>
+      </c>
+      <c r="O54">
+        <v>-17.48125634640919</v>
+      </c>
+      <c r="P54">
+        <v>-52.44376903922756</v>
+      </c>
+      <c r="Q54">
+        <v>-47.77376903922756</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1745108885753696</v>
+      </c>
+      <c r="T54">
+        <v>1.564731292336595</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.1054013592317249</v>
+      </c>
+      <c r="W54">
+        <v>0.2136301554154641</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.4216054369268996</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1968529073322187</v>
+      </c>
+      <c r="C55">
+        <v>-65.19969053947648</v>
+      </c>
+      <c r="D55">
+        <v>404.596665071813</v>
+      </c>
+      <c r="E55">
+        <v>502.9183261560264</v>
+      </c>
+      <c r="F55">
+        <v>515.9963556112895</v>
+      </c>
+      <c r="G55">
+        <v>46.2</v>
+      </c>
+      <c r="H55">
+        <v>960.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>55.64</v>
+      </c>
+      <c r="K55">
+        <v>4.67</v>
+      </c>
+      <c r="L55">
+        <v>50.97</v>
+      </c>
+      <c r="M55">
+        <v>123.2199297199759</v>
+      </c>
+      <c r="N55">
+        <v>-72.24992971997592</v>
+      </c>
+      <c r="O55">
+        <v>-18.06248242999398</v>
+      </c>
+      <c r="P55">
+        <v>-54.18744728998195</v>
+      </c>
+      <c r="Q55">
+        <v>-49.51744728998194</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1773983542897391</v>
+      </c>
+      <c r="T55">
+        <v>1.598023447492692</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.1034126543405603</v>
+      </c>
+      <c r="W55">
+        <v>0.2141050581434742</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.4136506173622411</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1988529073322187</v>
+      </c>
+      <c r="C56">
+        <v>-79.99125734632281</v>
+      </c>
+      <c r="D56">
+        <v>399.5408785595192</v>
+      </c>
+      <c r="E56">
+        <v>512.654106450579</v>
+      </c>
+      <c r="F56">
+        <v>525.732135905842</v>
+      </c>
+      <c r="G56">
+        <v>46.2</v>
+      </c>
+      <c r="H56">
+        <v>960.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>55.64</v>
+      </c>
+      <c r="K56">
+        <v>4.67</v>
+      </c>
+      <c r="L56">
+        <v>50.97</v>
+      </c>
+      <c r="M56">
+        <v>125.5448340543151</v>
+      </c>
+      <c r="N56">
+        <v>-74.57483405431509</v>
+      </c>
+      <c r="O56">
+        <v>-18.64370851357877</v>
+      </c>
+      <c r="P56">
+        <v>-55.93112554073632</v>
+      </c>
+      <c r="Q56">
+        <v>-51.26112554073632</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.18041136199169</v>
+      </c>
+      <c r="T56">
+        <v>1.632763087655577</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.1014976051861055</v>
+      </c>
+      <c r="W56">
+        <v>0.2145623718815581</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.4059904207444218</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2008529073322187</v>
+      </c>
+      <c r="C57">
+        <v>-94.65803067440913</v>
+      </c>
+      <c r="D57">
+        <v>394.6098855259856</v>
+      </c>
+      <c r="E57">
+        <v>522.3898867451317</v>
+      </c>
+      <c r="F57">
+        <v>535.4679162003947</v>
+      </c>
+      <c r="G57">
+        <v>46.2</v>
+      </c>
+      <c r="H57">
+        <v>960.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>55.64</v>
+      </c>
+      <c r="K57">
+        <v>4.67</v>
+      </c>
+      <c r="L57">
+        <v>50.97</v>
+      </c>
+      <c r="M57">
+        <v>127.8697383886543</v>
+      </c>
+      <c r="N57">
+        <v>-76.89973838865427</v>
+      </c>
+      <c r="O57">
+        <v>-19.22493459716357</v>
+      </c>
+      <c r="P57">
+        <v>-57.6748037914907</v>
+      </c>
+      <c r="Q57">
+        <v>-53.0048037914907</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1835582811470609</v>
+      </c>
+      <c r="T57">
+        <v>1.669046711825701</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.09965219418272171</v>
+      </c>
+      <c r="W57">
+        <v>0.2150030560291661</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3986087767308868</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2028529073322187</v>
+      </c>
+      <c r="C58">
+        <v>-109.2045746663935</v>
+      </c>
+      <c r="D58">
+        <v>389.799121828554</v>
+      </c>
+      <c r="E58">
+        <v>532.1256670396843</v>
+      </c>
+      <c r="F58">
+        <v>545.2036964949474</v>
+      </c>
+      <c r="G58">
+        <v>46.2</v>
+      </c>
+      <c r="H58">
+        <v>960.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>55.64</v>
+      </c>
+      <c r="K58">
+        <v>4.67</v>
+      </c>
+      <c r="L58">
+        <v>50.97</v>
+      </c>
+      <c r="M58">
+        <v>130.1946427229934</v>
+      </c>
+      <c r="N58">
+        <v>-79.22464272299345</v>
+      </c>
+      <c r="O58">
+        <v>-19.80616068074836</v>
+      </c>
+      <c r="P58">
+        <v>-59.41848204224509</v>
+      </c>
+      <c r="Q58">
+        <v>-54.74848204224509</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1868482420822214</v>
+      </c>
+      <c r="T58">
+        <v>1.706979591639922</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.0978726907151731</v>
+      </c>
+      <c r="W58">
+        <v>0.2154280014572167</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3914907628606924</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2048529073322187</v>
+      </c>
+      <c r="C59">
+        <v>-123.6352335763345</v>
+      </c>
+      <c r="D59">
+        <v>385.1042432131655</v>
+      </c>
+      <c r="E59">
+        <v>541.8614473342369</v>
+      </c>
+      <c r="F59">
+        <v>554.9394767895</v>
+      </c>
+      <c r="G59">
+        <v>46.2</v>
+      </c>
+      <c r="H59">
+        <v>960.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>55.64</v>
+      </c>
+      <c r="K59">
+        <v>4.67</v>
+      </c>
+      <c r="L59">
+        <v>50.97</v>
+      </c>
+      <c r="M59">
+        <v>132.5195470573326</v>
+      </c>
+      <c r="N59">
+        <v>-81.5495470573326</v>
+      </c>
+      <c r="O59">
+        <v>-20.38738676433315</v>
+      </c>
+      <c r="P59">
+        <v>-61.16216029299945</v>
+      </c>
+      <c r="Q59">
+        <v>-56.49216029299945</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1902912244562265</v>
+      </c>
+      <c r="T59">
+        <v>1.746676791445501</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.09615562596578411</v>
+      </c>
+      <c r="W59">
+        <v>0.2158380365193708</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.3846225038631365</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2068529073322187</v>
+      </c>
+      <c r="C60">
+        <v>-137.9541448541775</v>
+      </c>
+      <c r="D60">
+        <v>380.521112229875</v>
+      </c>
+      <c r="E60">
+        <v>551.5972276287895</v>
+      </c>
+      <c r="F60">
+        <v>564.6752570840525</v>
+      </c>
+      <c r="G60">
+        <v>46.2</v>
+      </c>
+      <c r="H60">
+        <v>960.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>55.64</v>
+      </c>
+      <c r="K60">
+        <v>4.67</v>
+      </c>
+      <c r="L60">
+        <v>50.97</v>
+      </c>
+      <c r="M60">
+        <v>134.8444513916718</v>
+      </c>
+      <c r="N60">
+        <v>-83.87445139167176</v>
+      </c>
+      <c r="O60">
+        <v>-20.96861284791794</v>
+      </c>
+      <c r="P60">
+        <v>-62.90583854375382</v>
+      </c>
+      <c r="Q60">
+        <v>-58.23583854375381</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1938981583718509</v>
+      </c>
+      <c r="T60">
+        <v>1.788264334098965</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.09449777034568439</v>
+      </c>
+      <c r="W60">
+        <v>0.2162339324414506</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3779910813827376</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2088529073322187</v>
+      </c>
+      <c r="C61">
+        <v>-152.1652513069179</v>
+      </c>
+      <c r="D61">
+        <v>376.0457860716874</v>
+      </c>
+      <c r="E61">
+        <v>561.3330079233422</v>
+      </c>
+      <c r="F61">
+        <v>574.4110373786052</v>
+      </c>
+      <c r="G61">
+        <v>46.2</v>
+      </c>
+      <c r="H61">
+        <v>960.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>55.64</v>
+      </c>
+      <c r="K61">
+        <v>4.67</v>
+      </c>
+      <c r="L61">
+        <v>50.97</v>
+      </c>
+      <c r="M61">
+        <v>137.1693557260109</v>
+      </c>
+      <c r="N61">
+        <v>-86.19935572601094</v>
+      </c>
+      <c r="O61">
+        <v>-21.54983893150273</v>
+      </c>
+      <c r="P61">
+        <v>-64.6495167945082</v>
+      </c>
+      <c r="Q61">
+        <v>-59.9795167945082</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1976810402833594</v>
+      </c>
+      <c r="T61">
+        <v>1.831880537369671</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.09289611322118126</v>
+      </c>
+      <c r="W61">
+        <v>0.2166164081627819</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3715844528847251</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2108529073322187</v>
+      </c>
+      <c r="C62">
+        <v>-166.2723124115712</v>
+      </c>
+      <c r="D62">
+        <v>371.6745052615866</v>
+      </c>
+      <c r="E62">
+        <v>571.0687882178947</v>
+      </c>
+      <c r="F62">
+        <v>584.1468176731578</v>
+      </c>
+      <c r="G62">
+        <v>46.2</v>
+      </c>
+      <c r="H62">
+        <v>960.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>55.64</v>
+      </c>
+      <c r="K62">
+        <v>4.67</v>
+      </c>
+      <c r="L62">
+        <v>50.97</v>
+      </c>
+      <c r="M62">
+        <v>139.4942600603501</v>
+      </c>
+      <c r="N62">
+        <v>-88.52426006035009</v>
+      </c>
+      <c r="O62">
+        <v>-22.13106501508752</v>
+      </c>
+      <c r="P62">
+        <v>-66.39319504526256</v>
+      </c>
+      <c r="Q62">
+        <v>-61.72319504526256</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2016530662904434</v>
+      </c>
+      <c r="T62">
+        <v>1.877677550803913</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.09134784466749492</v>
+      </c>
+      <c r="W62">
+        <v>0.2169861346934022</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3653913786699796</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2128529073322187</v>
+      </c>
+      <c r="C63">
+        <v>-180.2789148481771</v>
+      </c>
+      <c r="D63">
+        <v>367.4036831195334</v>
+      </c>
+      <c r="E63">
+        <v>580.8045685124474</v>
+      </c>
+      <c r="F63">
+        <v>593.8825979677105</v>
+      </c>
+      <c r="G63">
+        <v>46.2</v>
+      </c>
+      <c r="H63">
+        <v>960.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>55.64</v>
+      </c>
+      <c r="K63">
+        <v>4.67</v>
+      </c>
+      <c r="L63">
+        <v>50.97</v>
+      </c>
+      <c r="M63">
+        <v>141.8191643946893</v>
+      </c>
+      <c r="N63">
+        <v>-90.84916439468927</v>
+      </c>
+      <c r="O63">
+        <v>-22.71229109867232</v>
+      </c>
+      <c r="P63">
+        <v>-68.13687329601694</v>
+      </c>
+      <c r="Q63">
+        <v>-63.46687329601694</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2058287859389163</v>
+      </c>
+      <c r="T63">
+        <v>1.925823129029654</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.08985033901720811</v>
+      </c>
+      <c r="W63">
+        <v>0.2173437390426907</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3594013560688324</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2148529073322187</v>
+      </c>
+      <c r="C64">
+        <v>-194.1884823148578</v>
+      </c>
+      <c r="D64">
+        <v>363.2298959474053</v>
+      </c>
+      <c r="E64">
+        <v>590.540348807</v>
+      </c>
+      <c r="F64">
+        <v>603.618378262263</v>
+      </c>
+      <c r="G64">
+        <v>46.2</v>
+      </c>
+      <c r="H64">
+        <v>960.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>55.64</v>
+      </c>
+      <c r="K64">
+        <v>4.67</v>
+      </c>
+      <c r="L64">
+        <v>50.97</v>
+      </c>
+      <c r="M64">
+        <v>144.1440687290284</v>
+      </c>
+      <c r="N64">
+        <v>-93.17406872902842</v>
+      </c>
+      <c r="O64">
+        <v>-23.2935171822571</v>
+      </c>
+      <c r="P64">
+        <v>-69.88055154677131</v>
+      </c>
+      <c r="Q64">
+        <v>-65.21055154677131</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.21022428030573</v>
+      </c>
+      <c r="T64">
+        <v>1.976502685056751</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.08840114000080153</v>
+      </c>
+      <c r="W64">
+        <v>0.2176898077678086</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3536045600032062</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2168529073322187</v>
+      </c>
+      <c r="C65">
+        <v>-208.0042846813857</v>
+      </c>
+      <c r="D65">
+        <v>359.14987387543</v>
+      </c>
+      <c r="E65">
+        <v>600.2761291015527</v>
+      </c>
+      <c r="F65">
+        <v>613.3541585568157</v>
+      </c>
+      <c r="G65">
+        <v>46.2</v>
+      </c>
+      <c r="H65">
+        <v>960.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>55.64</v>
+      </c>
+      <c r="K65">
+        <v>4.67</v>
+      </c>
+      <c r="L65">
+        <v>50.97</v>
+      </c>
+      <c r="M65">
+        <v>146.4689730633676</v>
+      </c>
+      <c r="N65">
+        <v>-95.4989730633676</v>
+      </c>
+      <c r="O65">
+        <v>-23.8747432658419</v>
+      </c>
+      <c r="P65">
+        <v>-71.6242297975257</v>
+      </c>
+      <c r="Q65">
+        <v>-66.9542297975257</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2148573689626416</v>
+      </c>
+      <c r="T65">
+        <v>2.029921676544771</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.0869979473023761</v>
+      </c>
+      <c r="W65">
+        <v>0.2180248901841926</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3479917892095045</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2188529073322187</v>
+      </c>
+      <c r="C66">
+        <v>-221.7294465326912</v>
+      </c>
+      <c r="D66">
+        <v>355.1604923186773</v>
+      </c>
+      <c r="E66">
+        <v>610.0119093961054</v>
+      </c>
+      <c r="F66">
+        <v>623.0899388513684</v>
+      </c>
+      <c r="G66">
+        <v>46.2</v>
+      </c>
+      <c r="H66">
+        <v>960.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>55.64</v>
+      </c>
+      <c r="K66">
+        <v>4.67</v>
+      </c>
+      <c r="L66">
+        <v>50.97</v>
+      </c>
+      <c r="M66">
+        <v>148.7938773977068</v>
+      </c>
+      <c r="N66">
+        <v>-97.82387739770678</v>
+      </c>
+      <c r="O66">
+        <v>-24.4559693494267</v>
+      </c>
+      <c r="P66">
+        <v>-73.36790804828009</v>
+      </c>
+      <c r="Q66">
+        <v>-68.69790804828008</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2197478514338261</v>
+      </c>
+      <c r="T66">
+        <v>2.086308389782126</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.08563860437577647</v>
+      </c>
+      <c r="W66">
+        <v>0.2183495012750646</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3425544175031059</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2208529073322187</v>
+      </c>
+      <c r="C67">
+        <v>-235.366955149226</v>
+      </c>
+      <c r="D67">
+        <v>351.258763996695</v>
+      </c>
+      <c r="E67">
+        <v>619.7476896906579</v>
+      </c>
+      <c r="F67">
+        <v>632.825719145921</v>
+      </c>
+      <c r="G67">
+        <v>46.2</v>
+      </c>
+      <c r="H67">
+        <v>960.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>55.64</v>
+      </c>
+      <c r="K67">
+        <v>4.67</v>
+      </c>
+      <c r="L67">
+        <v>50.97</v>
+      </c>
+      <c r="M67">
+        <v>151.1187817320459</v>
+      </c>
+      <c r="N67">
+        <v>-100.1487817320459</v>
+      </c>
+      <c r="O67">
+        <v>-25.03719543301148</v>
+      </c>
+      <c r="P67">
+        <v>-75.11158629903446</v>
+      </c>
+      <c r="Q67">
+        <v>-70.44158629903446</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2249177900462211</v>
+      </c>
+      <c r="T67">
+        <v>2.145917200918758</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.08432108738537993</v>
+      </c>
+      <c r="W67">
+        <v>0.2186641243323713</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3372843495415196</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2228529073322187</v>
+      </c>
+      <c r="C68">
+        <v>-248.9196679670196</v>
+      </c>
+      <c r="D68">
+        <v>347.441831473454</v>
+      </c>
+      <c r="E68">
+        <v>629.4834699852106</v>
+      </c>
+      <c r="F68">
+        <v>642.5614994404737</v>
+      </c>
+      <c r="G68">
+        <v>46.2</v>
+      </c>
+      <c r="H68">
+        <v>960.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>55.64</v>
+      </c>
+      <c r="K68">
+        <v>4.67</v>
+      </c>
+      <c r="L68">
+        <v>50.97</v>
+      </c>
+      <c r="M68">
+        <v>153.4436860663851</v>
+      </c>
+      <c r="N68">
+        <v>-102.4736860663851</v>
+      </c>
+      <c r="O68">
+        <v>-25.61842151659628</v>
+      </c>
+      <c r="P68">
+        <v>-76.85526454978884</v>
+      </c>
+      <c r="Q68">
+        <v>-72.18526454978884</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2303918426946394</v>
+      </c>
+      <c r="T68">
+        <v>2.209032412710486</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0830434951522681</v>
+      </c>
+      <c r="W68">
+        <v>0.2189692133576384</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3321739806090724</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2248529073322187</v>
+      </c>
+      <c r="C69">
+        <v>-262.3903195565751</v>
+      </c>
+      <c r="D69">
+        <v>343.7069601784513</v>
+      </c>
+      <c r="E69">
+        <v>639.2192502797633</v>
+      </c>
+      <c r="F69">
+        <v>652.2972797350263</v>
+      </c>
+      <c r="G69">
+        <v>46.2</v>
+      </c>
+      <c r="H69">
+        <v>960.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>55.64</v>
+      </c>
+      <c r="K69">
+        <v>4.67</v>
+      </c>
+      <c r="L69">
+        <v>50.97</v>
+      </c>
+      <c r="M69">
+        <v>155.7685904007243</v>
+      </c>
+      <c r="N69">
+        <v>-104.7985904007243</v>
+      </c>
+      <c r="O69">
+        <v>-26.19964760018107</v>
+      </c>
+      <c r="P69">
+        <v>-78.59894280054323</v>
+      </c>
+      <c r="Q69">
+        <v>-73.92894280054323</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2361976561096285</v>
+      </c>
+      <c r="T69">
+        <v>2.275972788853228</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.08180404000074171</v>
+      </c>
+      <c r="W69">
+        <v>0.2192651952478229</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3272161600029668</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2268529073322187</v>
+      </c>
+      <c r="C70">
+        <v>-275.7815281564316</v>
+      </c>
+      <c r="D70">
+        <v>340.0515318731473</v>
+      </c>
+      <c r="E70">
+        <v>648.9550305743159</v>
+      </c>
+      <c r="F70">
+        <v>662.0330600295789</v>
+      </c>
+      <c r="G70">
+        <v>46.2</v>
+      </c>
+      <c r="H70">
+        <v>960.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>55.64</v>
+      </c>
+      <c r="K70">
+        <v>4.67</v>
+      </c>
+      <c r="L70">
+        <v>50.97</v>
+      </c>
+      <c r="M70">
+        <v>158.0934947350634</v>
+      </c>
+      <c r="N70">
+        <v>-107.1234947350634</v>
+      </c>
+      <c r="O70">
+        <v>-26.78087368376586</v>
+      </c>
+      <c r="P70">
+        <v>-80.34262105129758</v>
+      </c>
+      <c r="Q70">
+        <v>-75.67262105129758</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2423663328630543</v>
+      </c>
+      <c r="T70">
+        <v>2.347096938504892</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.08060103941249551</v>
+      </c>
+      <c r="W70">
+        <v>0.2195524717882961</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.322404157649982</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2288529073322187</v>
+      </c>
+      <c r="C71">
+        <v>-289.0958017941957</v>
+      </c>
+      <c r="D71">
+        <v>336.4730385299359</v>
+      </c>
+      <c r="E71">
+        <v>658.6908108688685</v>
+      </c>
+      <c r="F71">
+        <v>671.7688403241316</v>
+      </c>
+      <c r="G71">
+        <v>46.2</v>
+      </c>
+      <c r="H71">
+        <v>960.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>55.64</v>
+      </c>
+      <c r="K71">
+        <v>4.67</v>
+      </c>
+      <c r="L71">
+        <v>50.97</v>
+      </c>
+      <c r="M71">
+        <v>160.4183990694026</v>
+      </c>
+      <c r="N71">
+        <v>-109.4483990694026</v>
+      </c>
+      <c r="O71">
+        <v>-27.36209976735066</v>
+      </c>
+      <c r="P71">
+        <v>-82.08629930205197</v>
+      </c>
+      <c r="Q71">
+        <v>-77.41629930205197</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2489329887618626</v>
+      </c>
+      <c r="T71">
+        <v>2.422809742972792</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.0794329084065173</v>
+      </c>
+      <c r="W71">
+        <v>0.2198314214725237</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3177316336260693</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2308529073322187</v>
+      </c>
+      <c r="C72">
+        <v>-302.3355440251108</v>
+      </c>
+      <c r="D72">
+        <v>332.9690765935733</v>
+      </c>
+      <c r="E72">
+        <v>668.4265911634211</v>
+      </c>
+      <c r="F72">
+        <v>681.5046206186842</v>
+      </c>
+      <c r="G72">
+        <v>46.2</v>
+      </c>
+      <c r="H72">
+        <v>960.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>55.64</v>
+      </c>
+      <c r="K72">
+        <v>4.67</v>
+      </c>
+      <c r="L72">
+        <v>50.97</v>
+      </c>
+      <c r="M72">
+        <v>162.7433034037418</v>
+      </c>
+      <c r="N72">
+        <v>-111.7733034037418</v>
+      </c>
+      <c r="O72">
+        <v>-27.94332585093544</v>
+      </c>
+      <c r="P72">
+        <v>-83.82997755280633</v>
+      </c>
+      <c r="Q72">
+        <v>-79.15997755280632</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2559374217205913</v>
+      </c>
+      <c r="T72">
+        <v>2.503570067738552</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.0782981525721385</v>
+      </c>
+      <c r="W72">
+        <v>0.2201024011657733</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3131926102885539</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2328529073322187</v>
+      </c>
+      <c r="C73">
+        <v>-315.5030593157645</v>
+      </c>
+      <c r="D73">
+        <v>329.5373415974723</v>
+      </c>
+      <c r="E73">
+        <v>678.1623714579737</v>
+      </c>
+      <c r="F73">
+        <v>691.2404009132367</v>
+      </c>
+      <c r="G73">
+        <v>46.2</v>
+      </c>
+      <c r="H73">
+        <v>960.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>55.64</v>
+      </c>
+      <c r="K73">
+        <v>4.67</v>
+      </c>
+      <c r="L73">
+        <v>50.97</v>
+      </c>
+      <c r="M73">
+        <v>165.0682077380809</v>
+      </c>
+      <c r="N73">
+        <v>-114.0982077380809</v>
+      </c>
+      <c r="O73">
+        <v>-28.52455193452023</v>
+      </c>
+      <c r="P73">
+        <v>-85.5736558035607</v>
+      </c>
+      <c r="Q73">
+        <v>-80.9036558035607</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2634249190213013</v>
+      </c>
+      <c r="T73">
+        <v>2.589900070074363</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.07719536169084078</v>
+      </c>
+      <c r="W73">
+        <v>0.2203657476282272</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3087814467633631</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2348529073322187</v>
+      </c>
+      <c r="C74">
+        <v>-328.6005580982665</v>
+      </c>
+      <c r="D74">
+        <v>326.1756231095229</v>
+      </c>
+      <c r="E74">
+        <v>687.8981517525264</v>
+      </c>
+      <c r="F74">
+        <v>700.9761812077894</v>
+      </c>
+      <c r="G74">
+        <v>46.2</v>
+      </c>
+      <c r="H74">
+        <v>960.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>55.64</v>
+      </c>
+      <c r="K74">
+        <v>4.67</v>
+      </c>
+      <c r="L74">
+        <v>50.97</v>
+      </c>
+      <c r="M74">
+        <v>167.3931120724201</v>
+      </c>
+      <c r="N74">
+        <v>-116.4231120724201</v>
+      </c>
+      <c r="O74">
+        <v>-29.10577801810503</v>
+      </c>
+      <c r="P74">
+        <v>-87.31733405431508</v>
+      </c>
+      <c r="Q74">
+        <v>-82.64733405431508</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2714472375577763</v>
+      </c>
+      <c r="T74">
+        <v>2.682396501148447</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.07612320388957909</v>
+      </c>
+      <c r="W74">
+        <v>0.2206217789111685</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3044928155583164</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2368529073322187</v>
+      </c>
+      <c r="C75">
+        <v>-341.6301615181962</v>
+      </c>
+      <c r="D75">
+        <v>322.8817999841457</v>
+      </c>
+      <c r="E75">
+        <v>697.6339320470789</v>
+      </c>
+      <c r="F75">
+        <v>710.711961502342</v>
+      </c>
+      <c r="G75">
+        <v>46.2</v>
+      </c>
+      <c r="H75">
+        <v>960.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>55.64</v>
+      </c>
+      <c r="K75">
+        <v>4.67</v>
+      </c>
+      <c r="L75">
+        <v>50.97</v>
+      </c>
+      <c r="M75">
+        <v>169.7180164067593</v>
+      </c>
+      <c r="N75">
+        <v>-118.7480164067593</v>
+      </c>
+      <c r="O75">
+        <v>-29.68700410168982</v>
+      </c>
+      <c r="P75">
+        <v>-89.06101230506945</v>
+      </c>
+      <c r="Q75">
+        <v>-84.39101230506945</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2800638019117681</v>
+      </c>
+      <c r="T75">
+        <v>2.781744519709501</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.07508042027465336</v>
+      </c>
+      <c r="W75">
+        <v>0.2208707956384128</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3003216810986135</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2388529073322187</v>
+      </c>
+      <c r="C76">
+        <v>-354.5939058977493</v>
+      </c>
+      <c r="D76">
+        <v>319.6538358991454</v>
+      </c>
+      <c r="E76">
+        <v>707.3697123416316</v>
+      </c>
+      <c r="F76">
+        <v>720.4477417968947</v>
+      </c>
+      <c r="G76">
+        <v>46.2</v>
+      </c>
+      <c r="H76">
+        <v>960.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>55.64</v>
+      </c>
+      <c r="K76">
+        <v>4.67</v>
+      </c>
+      <c r="L76">
+        <v>50.97</v>
+      </c>
+      <c r="M76">
+        <v>172.0429207410984</v>
+      </c>
+      <c r="N76">
+        <v>-121.0729207410984</v>
+      </c>
+      <c r="O76">
+        <v>-30.26823018527461</v>
+      </c>
+      <c r="P76">
+        <v>-90.80469055582384</v>
+      </c>
+      <c r="Q76">
+        <v>-86.13469055582384</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2893431789083745</v>
+      </c>
+      <c r="T76">
+        <v>2.888734693544482</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.07406582000067155</v>
+      </c>
+      <c r="W76">
+        <v>0.2211130821838397</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2962632800026862</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2408529073322187</v>
+      </c>
+      <c r="C77">
+        <v>-367.4937469338141</v>
+      </c>
+      <c r="D77">
+        <v>316.4897751576331</v>
+      </c>
+      <c r="E77">
+        <v>717.1054926361842</v>
+      </c>
+      <c r="F77">
+        <v>730.1835220914472</v>
+      </c>
+      <c r="G77">
+        <v>46.2</v>
+      </c>
+      <c r="H77">
+        <v>960.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>55.64</v>
+      </c>
+      <c r="K77">
+        <v>4.67</v>
+      </c>
+      <c r="L77">
+        <v>50.97</v>
+      </c>
+      <c r="M77">
+        <v>174.3678250754376</v>
+      </c>
+      <c r="N77">
+        <v>-123.3978250754376</v>
+      </c>
+      <c r="O77">
+        <v>-30.8494562688594</v>
+      </c>
+      <c r="P77">
+        <v>-92.5483688065782</v>
+      </c>
+      <c r="Q77">
+        <v>-87.87836880657819</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2993649060647095</v>
+      </c>
+      <c r="T77">
+        <v>3.004284081286261</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.07307827573399595</v>
+      </c>
+      <c r="W77">
+        <v>0.2213489077547218</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2923131029359838</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2428529073322187</v>
+      </c>
+      <c r="C78">
+        <v>-380.3315636491697</v>
+      </c>
+      <c r="D78">
+        <v>313.3877387368302</v>
+      </c>
+      <c r="E78">
+        <v>726.8412729307369</v>
+      </c>
+      <c r="F78">
+        <v>739.9193023859999</v>
+      </c>
+      <c r="G78">
+        <v>46.2</v>
+      </c>
+      <c r="H78">
+        <v>960.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>55.64</v>
+      </c>
+      <c r="K78">
+        <v>4.67</v>
+      </c>
+      <c r="L78">
+        <v>50.97</v>
+      </c>
+      <c r="M78">
+        <v>176.6927294097768</v>
+      </c>
+      <c r="N78">
+        <v>-125.7227294097768</v>
+      </c>
+      <c r="O78">
+        <v>-31.43068235244419</v>
+      </c>
+      <c r="P78">
+        <v>-94.29204705733258</v>
+      </c>
+      <c r="Q78">
+        <v>-89.62204705733258</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3102217771507391</v>
+      </c>
+      <c r="T78">
+        <v>3.129462584673189</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.07211671947433809</v>
+      </c>
+      <c r="W78">
+        <v>0.2215785273895281</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2884668778973524</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2448529073322187</v>
+      </c>
+      <c r="C79">
+        <v>-393.1091621135728</v>
+      </c>
+      <c r="D79">
+        <v>310.3459205669798</v>
+      </c>
+      <c r="E79">
+        <v>736.5770532252895</v>
+      </c>
+      <c r="F79">
+        <v>749.6550826805526</v>
+      </c>
+      <c r="G79">
+        <v>46.2</v>
+      </c>
+      <c r="H79">
+        <v>960.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>55.64</v>
+      </c>
+      <c r="K79">
+        <v>4.67</v>
+      </c>
+      <c r="L79">
+        <v>50.97</v>
+      </c>
+      <c r="M79">
+        <v>179.017633744116</v>
+      </c>
+      <c r="N79">
+        <v>-128.047633744116</v>
+      </c>
+      <c r="O79">
+        <v>-32.011908436029</v>
+      </c>
+      <c r="P79">
+        <v>-96.035725308087</v>
+      </c>
+      <c r="Q79">
+        <v>-91.36572530808699</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3220227239833799</v>
+      </c>
+      <c r="T79">
+        <v>3.265526175311154</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.07118013870194408</v>
+      </c>
+      <c r="W79">
+        <v>0.2218021828779758</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2847205548077762</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2468529073322187</v>
+      </c>
+      <c r="C80">
+        <v>-405.8282789502236</v>
+      </c>
+      <c r="D80">
+        <v>307.3625840248816</v>
+      </c>
+      <c r="E80">
+        <v>746.3128335198421</v>
+      </c>
+      <c r="F80">
+        <v>759.3908629751052</v>
+      </c>
+      <c r="G80">
+        <v>46.2</v>
+      </c>
+      <c r="H80">
+        <v>960.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>55.64</v>
+      </c>
+      <c r="K80">
+        <v>4.67</v>
+      </c>
+      <c r="L80">
+        <v>50.97</v>
+      </c>
+      <c r="M80">
+        <v>181.3425380784551</v>
+      </c>
+      <c r="N80">
+        <v>-130.3725380784551</v>
+      </c>
+      <c r="O80">
+        <v>-32.59313451961378</v>
+      </c>
+      <c r="P80">
+        <v>-97.77940355884135</v>
+      </c>
+      <c r="Q80">
+        <v>-93.10940355884135</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3348964841644427</v>
+      </c>
+      <c r="T80">
+        <v>3.413959183279843</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.07026757282114993</v>
+      </c>
+      <c r="W80">
+        <v>0.2220201036103094</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2810702912845997</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2488529073322187</v>
+      </c>
+      <c r="C81">
+        <v>-418.4905846419112</v>
+      </c>
+      <c r="D81">
+        <v>304.4360586277467</v>
+      </c>
+      <c r="E81">
+        <v>756.0486138143948</v>
+      </c>
+      <c r="F81">
+        <v>769.1266432696578</v>
+      </c>
+      <c r="G81">
+        <v>46.2</v>
+      </c>
+      <c r="H81">
+        <v>960.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>55.64</v>
+      </c>
+      <c r="K81">
+        <v>4.67</v>
+      </c>
+      <c r="L81">
+        <v>50.97</v>
+      </c>
+      <c r="M81">
+        <v>183.6674424127943</v>
+      </c>
+      <c r="N81">
+        <v>-132.6974424127943</v>
+      </c>
+      <c r="O81">
+        <v>-33.17436060319858</v>
+      </c>
+      <c r="P81">
+        <v>-99.52308180959574</v>
+      </c>
+      <c r="Q81">
+        <v>-94.85308180959574</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3489963167437019</v>
+      </c>
+      <c r="T81">
+        <v>3.576528668197931</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.06937810987404676</v>
+      </c>
+      <c r="W81">
+        <v>0.2222325073620776</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.277512439496187</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2508529073322187</v>
+      </c>
+      <c r="C82">
+        <v>-431.0976866500661</v>
+      </c>
+      <c r="D82">
+        <v>301.5647369141444</v>
+      </c>
+      <c r="E82">
+        <v>765.7843941089475</v>
+      </c>
+      <c r="F82">
+        <v>778.8624235642105</v>
+      </c>
+      <c r="G82">
+        <v>46.2</v>
+      </c>
+      <c r="H82">
+        <v>960.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>55.64</v>
+      </c>
+      <c r="K82">
+        <v>4.67</v>
+      </c>
+      <c r="L82">
+        <v>50.97</v>
+      </c>
+      <c r="M82">
+        <v>185.9923467471335</v>
+      </c>
+      <c r="N82">
+        <v>-135.0223467471335</v>
+      </c>
+      <c r="O82">
+        <v>-33.75558668678337</v>
+      </c>
+      <c r="P82">
+        <v>-101.2667600603501</v>
+      </c>
+      <c r="Q82">
+        <v>-96.59676006035012</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.364506132580887</v>
+      </c>
+      <c r="T82">
+        <v>3.755355101607827</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.06851088350062116</v>
+      </c>
+      <c r="W82">
+        <v>0.2224396010200517</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2740435340024847</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2528529073322187</v>
+      </c>
+      <c r="C83">
+        <v>-443.6511323589557</v>
+      </c>
+      <c r="D83">
+        <v>298.7470714998074</v>
+      </c>
+      <c r="E83">
+        <v>775.5201744035001</v>
+      </c>
+      <c r="F83">
+        <v>788.5982038587631</v>
+      </c>
+      <c r="G83">
+        <v>46.2</v>
+      </c>
+      <c r="H83">
+        <v>960.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>55.64</v>
+      </c>
+      <c r="K83">
+        <v>4.67</v>
+      </c>
+      <c r="L83">
+        <v>50.97</v>
+      </c>
+      <c r="M83">
+        <v>188.3172510814726</v>
+      </c>
+      <c r="N83">
+        <v>-137.3472510814726</v>
+      </c>
+      <c r="O83">
+        <v>-34.33681277036816</v>
+      </c>
+      <c r="P83">
+        <v>-103.0104383111045</v>
+      </c>
+      <c r="Q83">
+        <v>-98.34043831110448</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.38164856061146</v>
+      </c>
+      <c r="T83">
+        <v>3.953005370113503</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.0676650701240703</v>
+      </c>
+      <c r="W83">
+        <v>0.222641581254372</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2706602804962812</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2548529073322187</v>
+      </c>
+      <c r="C84">
+        <v>-456.1524118563535</v>
+      </c>
+      <c r="D84">
+        <v>295.9815722969623</v>
+      </c>
+      <c r="E84">
+        <v>785.2559546980527</v>
+      </c>
+      <c r="F84">
+        <v>798.3339841533158</v>
+      </c>
+      <c r="G84">
+        <v>46.2</v>
+      </c>
+      <c r="H84">
+        <v>960.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>55.64</v>
+      </c>
+      <c r="K84">
+        <v>4.67</v>
+      </c>
+      <c r="L84">
+        <v>50.97</v>
+      </c>
+      <c r="M84">
+        <v>190.6421554158118</v>
+      </c>
+      <c r="N84">
+        <v>-139.6721554158118</v>
+      </c>
+      <c r="O84">
+        <v>-34.91803885395296</v>
+      </c>
+      <c r="P84">
+        <v>-104.7541165618589</v>
+      </c>
+      <c r="Q84">
+        <v>-100.0841165618589</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4006957028676522</v>
+      </c>
+      <c r="T84">
+        <v>4.172616779564253</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.06683988634206943</v>
+      </c>
+      <c r="W84">
+        <v>0.2228386351415138</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2673595453682778</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2568529073322187</v>
+      </c>
+      <c r="C85">
+        <v>-468.6029605611802</v>
+      </c>
+      <c r="D85">
+        <v>293.2668038866882</v>
+      </c>
+      <c r="E85">
+        <v>794.9917349926053</v>
+      </c>
+      <c r="F85">
+        <v>808.0697644478684</v>
+      </c>
+      <c r="G85">
+        <v>46.2</v>
+      </c>
+      <c r="H85">
+        <v>960.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>55.64</v>
+      </c>
+      <c r="K85">
+        <v>4.67</v>
+      </c>
+      <c r="L85">
+        <v>50.97</v>
+      </c>
+      <c r="M85">
+        <v>192.967059750151</v>
+      </c>
+      <c r="N85">
+        <v>-141.997059750151</v>
+      </c>
+      <c r="O85">
+        <v>-35.49926493753775</v>
+      </c>
+      <c r="P85">
+        <v>-106.4977948126132</v>
+      </c>
+      <c r="Q85">
+        <v>-101.8277948126132</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4219836853892788</v>
+      </c>
+      <c r="T85">
+        <v>4.418064825420974</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.06603458650662282</v>
+      </c>
+      <c r="W85">
+        <v>0.2230309407422185</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2641383460264913</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2588529073322187</v>
+      </c>
+      <c r="C86">
+        <v>-481.0041617078548</v>
+      </c>
+      <c r="D86">
+        <v>290.6013830345661</v>
+      </c>
+      <c r="E86">
+        <v>804.7275152871579</v>
+      </c>
+      <c r="F86">
+        <v>817.8055447424209</v>
+      </c>
+      <c r="G86">
+        <v>46.2</v>
+      </c>
+      <c r="H86">
+        <v>960.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>55.64</v>
+      </c>
+      <c r="K86">
+        <v>4.67</v>
+      </c>
+      <c r="L86">
+        <v>50.97</v>
+      </c>
+      <c r="M86">
+        <v>195.2919640844901</v>
+      </c>
+      <c r="N86">
+        <v>-144.3219640844901</v>
+      </c>
+      <c r="O86">
+        <v>-36.08049102112253</v>
+      </c>
+      <c r="P86">
+        <v>-108.2414730633676</v>
+      </c>
+      <c r="Q86">
+        <v>-103.5714730633676</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4459326657261086</v>
+      </c>
+      <c r="T86">
+        <v>4.694193877009782</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.06524846047678208</v>
+      </c>
+      <c r="W86">
+        <v>0.2232186676381444</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2609938419071283</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2608529073322187</v>
+      </c>
+      <c r="C87">
+        <v>-493.3573486963877</v>
+      </c>
+      <c r="D87">
+        <v>287.9839763405859</v>
+      </c>
+      <c r="E87">
+        <v>814.4632955817106</v>
+      </c>
+      <c r="F87">
+        <v>827.5413250369736</v>
+      </c>
+      <c r="G87">
+        <v>46.2</v>
+      </c>
+      <c r="H87">
+        <v>960.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>55.64</v>
+      </c>
+      <c r="K87">
+        <v>4.67</v>
+      </c>
+      <c r="L87">
+        <v>50.97</v>
+      </c>
+      <c r="M87">
+        <v>197.6168684188293</v>
+      </c>
+      <c r="N87">
+        <v>-146.6468684188293</v>
+      </c>
+      <c r="O87">
+        <v>-36.66171710470733</v>
+      </c>
+      <c r="P87">
+        <v>-109.985151314122</v>
+      </c>
+      <c r="Q87">
+        <v>-105.315151314122</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4730748434411825</v>
+      </c>
+      <c r="T87">
+        <v>5.007140135477101</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.06448083152999641</v>
+      </c>
+      <c r="W87">
+        <v>0.2234019774306369</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2579233261199856</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2628529073322187</v>
+      </c>
+      <c r="C88">
+        <v>-505.6638073166053</v>
+      </c>
+      <c r="D88">
+        <v>285.4132980149209</v>
+      </c>
+      <c r="E88">
+        <v>824.1990758762631</v>
+      </c>
+      <c r="F88">
+        <v>837.2771053315262</v>
+      </c>
+      <c r="G88">
+        <v>46.2</v>
+      </c>
+      <c r="H88">
+        <v>960.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>55.64</v>
+      </c>
+      <c r="K88">
+        <v>4.67</v>
+      </c>
+      <c r="L88">
+        <v>50.97</v>
+      </c>
+      <c r="M88">
+        <v>199.9417727531685</v>
+      </c>
+      <c r="N88">
+        <v>-148.9717727531685</v>
+      </c>
+      <c r="O88">
+        <v>-37.24294318829212</v>
+      </c>
+      <c r="P88">
+        <v>-111.7288295648763</v>
+      </c>
+      <c r="Q88">
+        <v>-107.0588295648763</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5040944751155527</v>
+      </c>
+      <c r="T88">
+        <v>5.364793002296895</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.0637310544191825</v>
+      </c>
+      <c r="W88">
+        <v>0.2235810242046992</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.25492421767673</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2648529073322187</v>
+      </c>
+      <c r="C89">
+        <v>-517.9247778543029</v>
+      </c>
+      <c r="D89">
+        <v>282.888107771776</v>
+      </c>
+      <c r="E89">
+        <v>833.9348561708158</v>
+      </c>
+      <c r="F89">
+        <v>847.0128856260789</v>
+      </c>
+      <c r="G89">
+        <v>46.2</v>
+      </c>
+      <c r="H89">
+        <v>960.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>55.64</v>
+      </c>
+      <c r="K89">
+        <v>4.67</v>
+      </c>
+      <c r="L89">
+        <v>50.97</v>
+      </c>
+      <c r="M89">
+        <v>202.2666770875076</v>
+      </c>
+      <c r="N89">
+        <v>-151.2966770875076</v>
+      </c>
+      <c r="O89">
+        <v>-37.82416927187691</v>
+      </c>
+      <c r="P89">
+        <v>-113.4725078156307</v>
+      </c>
+      <c r="Q89">
+        <v>-108.8025078156307</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.539886357816749</v>
+      </c>
+      <c r="T89">
+        <v>5.777469387088964</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.06299851356378959</v>
+      </c>
+      <c r="W89">
+        <v>0.2237559549609671</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2519940542551584</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2668529073322187</v>
+      </c>
+      <c r="C90">
+        <v>-530.1414570865716</v>
+      </c>
+      <c r="D90">
+        <v>280.4072088340599</v>
+      </c>
+      <c r="E90">
+        <v>843.6706364653685</v>
+      </c>
+      <c r="F90">
+        <v>856.7486659206315</v>
+      </c>
+      <c r="G90">
+        <v>46.2</v>
+      </c>
+      <c r="H90">
+        <v>960.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>55.64</v>
+      </c>
+      <c r="K90">
+        <v>4.67</v>
+      </c>
+      <c r="L90">
+        <v>50.97</v>
+      </c>
+      <c r="M90">
+        <v>204.5915814218468</v>
+      </c>
+      <c r="N90">
+        <v>-153.6215814218468</v>
+      </c>
+      <c r="O90">
+        <v>-38.40539535546171</v>
+      </c>
+      <c r="P90">
+        <v>-115.2161860663851</v>
+      </c>
+      <c r="Q90">
+        <v>-110.5461860663851</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5816435543014782</v>
+      </c>
+      <c r="T90">
+        <v>6.258925169346378</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.06228262136420107</v>
+      </c>
+      <c r="W90">
+        <v>0.2239269100182288</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2491304854568043</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2688529073322187</v>
+      </c>
+      <c r="C91">
+        <v>-542.3150001730469</v>
+      </c>
+      <c r="D91">
+        <v>277.9694460421373</v>
+      </c>
+      <c r="E91">
+        <v>853.4064167599211</v>
+      </c>
+      <c r="F91">
+        <v>866.4844462151841</v>
+      </c>
+      <c r="G91">
+        <v>46.2</v>
+      </c>
+      <c r="H91">
+        <v>960.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>55.64</v>
+      </c>
+      <c r="K91">
+        <v>4.67</v>
+      </c>
+      <c r="L91">
+        <v>50.97</v>
+      </c>
+      <c r="M91">
+        <v>206.916485756186</v>
+      </c>
+      <c r="N91">
+        <v>-155.946485756186</v>
+      </c>
+      <c r="O91">
+        <v>-38.98662143904649</v>
+      </c>
+      <c r="P91">
+        <v>-116.9598643171395</v>
+      </c>
+      <c r="Q91">
+        <v>-112.2898643171395</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6309929683288855</v>
+      </c>
+      <c r="T91">
+        <v>6.827918366559686</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.06158281662977185</v>
+      </c>
+      <c r="W91">
+        <v>0.2240940233888105</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2463312665190874</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2708529073322187</v>
+      </c>
+      <c r="C92">
+        <v>-554.4465224493551</v>
+      </c>
+      <c r="D92">
+        <v>275.5737040603816</v>
+      </c>
+      <c r="E92">
+        <v>863.1421970544737</v>
+      </c>
+      <c r="F92">
+        <v>876.2202265097368</v>
+      </c>
+      <c r="G92">
+        <v>46.2</v>
+      </c>
+      <c r="H92">
+        <v>960.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>55.64</v>
+      </c>
+      <c r="K92">
+        <v>4.67</v>
+      </c>
+      <c r="L92">
+        <v>50.97</v>
+      </c>
+      <c r="M92">
+        <v>209.2413900905252</v>
+      </c>
+      <c r="N92">
+        <v>-158.2713900905252</v>
+      </c>
+      <c r="O92">
+        <v>-39.56784752263129</v>
+      </c>
+      <c r="P92">
+        <v>-118.7035425678939</v>
+      </c>
+      <c r="Q92">
+        <v>-114.0335425678939</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6902122651617739</v>
+      </c>
+      <c r="T92">
+        <v>7.510710203215655</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.06089856311166327</v>
+      </c>
+      <c r="W92">
+        <v>0.2242574231289348</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2435942524466531</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2728529073322187</v>
+      </c>
+      <c r="C93">
+        <v>-566.5371011286101</v>
+      </c>
+      <c r="D93">
+        <v>273.2189056756793</v>
+      </c>
+      <c r="E93">
+        <v>872.8779773490263</v>
+      </c>
+      <c r="F93">
+        <v>885.9560068042894</v>
+      </c>
+      <c r="G93">
+        <v>46.2</v>
+      </c>
+      <c r="H93">
+        <v>960.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>55.64</v>
+      </c>
+      <c r="K93">
+        <v>4.67</v>
+      </c>
+      <c r="L93">
+        <v>50.97</v>
+      </c>
+      <c r="M93">
+        <v>211.5662944248643</v>
+      </c>
+      <c r="N93">
+        <v>-160.5962944248643</v>
+      </c>
+      <c r="O93">
+        <v>-40.14907360621608</v>
+      </c>
+      <c r="P93">
+        <v>-120.4472208186482</v>
+      </c>
+      <c r="Q93">
+        <v>-115.7772208186482</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7625914057353045</v>
+      </c>
+      <c r="T93">
+        <v>8.345233559128506</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.06022934813241423</v>
+      </c>
+      <c r="W93">
+        <v>0.2244172316659795</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2409173925296569</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2748529073322188</v>
+      </c>
+      <c r="C94">
+        <v>-578.5877769164103</v>
+      </c>
+      <c r="D94">
+        <v>270.9040101824316</v>
+      </c>
+      <c r="E94">
+        <v>882.613757643579</v>
+      </c>
+      <c r="F94">
+        <v>895.691787098842</v>
+      </c>
+      <c r="G94">
+        <v>46.2</v>
+      </c>
+      <c r="H94">
+        <v>960.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>55.64</v>
+      </c>
+      <c r="K94">
+        <v>4.67</v>
+      </c>
+      <c r="L94">
+        <v>50.97</v>
+      </c>
+      <c r="M94">
+        <v>213.8911987592035</v>
+      </c>
+      <c r="N94">
+        <v>-162.9211987592035</v>
+      </c>
+      <c r="O94">
+        <v>-40.73029968980087</v>
+      </c>
+      <c r="P94">
+        <v>-122.1908990694026</v>
+      </c>
+      <c r="Q94">
+        <v>-117.5208990694026</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8530653314522179</v>
+      </c>
+      <c r="T94">
+        <v>9.388387754019572</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05957468130488798</v>
+      </c>
+      <c r="W94">
+        <v>0.2245735661043928</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.238298725219552</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2768529073322187</v>
+      </c>
+      <c r="C95">
+        <v>-590.599555544429</v>
+      </c>
+      <c r="D95">
+        <v>268.6280118489657</v>
+      </c>
+      <c r="E95">
+        <v>892.3495379381317</v>
+      </c>
+      <c r="F95">
+        <v>905.4275673933947</v>
+      </c>
+      <c r="G95">
+        <v>46.2</v>
+      </c>
+      <c r="H95">
+        <v>960.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>55.64</v>
+      </c>
+      <c r="K95">
+        <v>4.67</v>
+      </c>
+      <c r="L95">
+        <v>50.97</v>
+      </c>
+      <c r="M95">
+        <v>216.2161030935427</v>
+      </c>
+      <c r="N95">
+        <v>-165.2461030935427</v>
+      </c>
+      <c r="O95">
+        <v>-41.31152577338567</v>
+      </c>
+      <c r="P95">
+        <v>-123.934577320157</v>
+      </c>
+      <c r="Q95">
+        <v>-119.264577320157</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9693889502311062</v>
+      </c>
+      <c r="T95">
+        <v>10.7295860045938</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.05893409333386768</v>
+      </c>
+      <c r="W95">
+        <v>0.2247265385118724</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2357363733354707</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2788529073322187</v>
+      </c>
+      <c r="C96">
+        <v>-602.5734092273384</v>
+      </c>
+      <c r="D96">
+        <v>266.3899384606089</v>
+      </c>
+      <c r="E96">
+        <v>902.0853182326842</v>
+      </c>
+      <c r="F96">
+        <v>915.1633476879473</v>
+      </c>
+      <c r="G96">
+        <v>46.2</v>
+      </c>
+      <c r="H96">
+        <v>960.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>55.64</v>
+      </c>
+      <c r="K96">
+        <v>4.67</v>
+      </c>
+      <c r="L96">
+        <v>50.97</v>
+      </c>
+      <c r="M96">
+        <v>218.5410074278818</v>
+      </c>
+      <c r="N96">
+        <v>-167.5710074278818</v>
+      </c>
+      <c r="O96">
+        <v>-41.89275185697046</v>
+      </c>
+      <c r="P96">
+        <v>-125.6782555709114</v>
+      </c>
+      <c r="Q96">
+        <v>-121.0082555709114</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.124487108602957</v>
+      </c>
+      <c r="T96">
+        <v>12.51785033869277</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.05830713489414568</v>
+      </c>
+      <c r="W96">
+        <v>0.224876256187278</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2332285395765827</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2808529073322188</v>
+      </c>
+      <c r="C97">
+        <v>-614.5102780475083</v>
+      </c>
+      <c r="D97">
+        <v>264.1888499349916</v>
+      </c>
+      <c r="E97">
+        <v>911.8210985272369</v>
+      </c>
+      <c r="F97">
+        <v>924.8991279825</v>
+      </c>
+      <c r="G97">
+        <v>46.2</v>
+      </c>
+      <c r="H97">
+        <v>960.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>55.64</v>
+      </c>
+      <c r="K97">
+        <v>4.67</v>
+      </c>
+      <c r="L97">
+        <v>50.97</v>
+      </c>
+      <c r="M97">
+        <v>220.865911762221</v>
+      </c>
+      <c r="N97">
+        <v>-169.895911762221</v>
+      </c>
+      <c r="O97">
+        <v>-42.47397794055525</v>
+      </c>
+      <c r="P97">
+        <v>-127.4219338216658</v>
+      </c>
+      <c r="Q97">
+        <v>-122.7519338216658</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.34162453032355</v>
+      </c>
+      <c r="T97">
+        <v>15.02142040643133</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.05769337557947046</v>
+      </c>
+      <c r="W97">
+        <v>0.2250228219116225</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2307735023178819</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2828529073322187</v>
+      </c>
+      <c r="C98">
+        <v>-626.4110712716168</v>
+      </c>
+      <c r="D98">
+        <v>262.0238370054357</v>
+      </c>
+      <c r="E98">
+        <v>921.5568788217895</v>
+      </c>
+      <c r="F98">
+        <v>934.6349082770525</v>
+      </c>
+      <c r="G98">
+        <v>46.2</v>
+      </c>
+      <c r="H98">
+        <v>960.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>55.64</v>
+      </c>
+      <c r="K98">
+        <v>4.67</v>
+      </c>
+      <c r="L98">
+        <v>50.97</v>
+      </c>
+      <c r="M98">
+        <v>223.1908160965602</v>
+      </c>
+      <c r="N98">
+        <v>-172.2208160965602</v>
+      </c>
+      <c r="O98">
+        <v>-43.05520402414004</v>
+      </c>
+      <c r="P98">
+        <v>-129.1656120724201</v>
+      </c>
+      <c r="Q98">
+        <v>-124.4956120724201</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.667330662904433</v>
+      </c>
+      <c r="T98">
+        <v>18.77677550803912</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.05709240291718432</v>
+      </c>
+      <c r="W98">
+        <v>0.2251663341833764</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2283696116687373</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2848529073322187</v>
+      </c>
+      <c r="C99">
+        <v>-638.2766686030529</v>
+      </c>
+      <c r="D99">
+        <v>259.8940199685522</v>
+      </c>
+      <c r="E99">
+        <v>931.2926591163421</v>
+      </c>
+      <c r="F99">
+        <v>944.3706885716051</v>
+      </c>
+      <c r="G99">
+        <v>46.2</v>
+      </c>
+      <c r="H99">
+        <v>960.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>55.64</v>
+      </c>
+      <c r="K99">
+        <v>4.67</v>
+      </c>
+      <c r="L99">
+        <v>50.97</v>
+      </c>
+      <c r="M99">
+        <v>225.5157204308993</v>
+      </c>
+      <c r="N99">
+        <v>-174.5457204308993</v>
+      </c>
+      <c r="O99">
+        <v>-43.63643010772483</v>
+      </c>
+      <c r="P99">
+        <v>-130.9092903231745</v>
+      </c>
+      <c r="Q99">
+        <v>-126.2392903231745</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.210174217205911</v>
+      </c>
+      <c r="T99">
+        <v>25.03570067738549</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05650382144381129</v>
+      </c>
+      <c r="W99">
+        <v>0.2253068874392179</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2260152857752451</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2868529073322187</v>
+      </c>
+      <c r="C100">
+        <v>-650.1079213737291</v>
+      </c>
+      <c r="D100">
+        <v>257.7985474924286</v>
+      </c>
+      <c r="E100">
+        <v>941.0284394108947</v>
+      </c>
+      <c r="F100">
+        <v>954.1064688661578</v>
+      </c>
+      <c r="G100">
+        <v>46.2</v>
+      </c>
+      <c r="H100">
+        <v>960.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>55.64</v>
+      </c>
+      <c r="K100">
+        <v>4.67</v>
+      </c>
+      <c r="L100">
+        <v>50.97</v>
+      </c>
+      <c r="M100">
+        <v>227.8406247652385</v>
+      </c>
+      <c r="N100">
+        <v>-176.8706247652385</v>
+      </c>
+      <c r="O100">
+        <v>-44.21765619130962</v>
+      </c>
+      <c r="P100">
+        <v>-132.6529685739289</v>
+      </c>
+      <c r="Q100">
+        <v>-127.9829685739289</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.295861325808866</v>
+      </c>
+      <c r="T100">
+        <v>37.55355101607823</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.05592725183724178</v>
+      </c>
+      <c r="W100">
+        <v>0.2254445722612667</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2237090073489671</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2888529073322187</v>
+      </c>
+      <c r="C101">
+        <v>-661.9056536787011</v>
+      </c>
+      <c r="D101">
+        <v>255.7365954820093</v>
+      </c>
+      <c r="E101">
+        <v>950.7642197054473</v>
+      </c>
+      <c r="F101">
+        <v>963.8422491607104</v>
+      </c>
+      <c r="G101">
+        <v>46.2</v>
+      </c>
+      <c r="H101">
+        <v>960.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>55.64</v>
+      </c>
+      <c r="K101">
+        <v>4.67</v>
+      </c>
+      <c r="L101">
+        <v>50.97</v>
+      </c>
+      <c r="M101">
+        <v>230.1655290995776</v>
+      </c>
+      <c r="N101">
+        <v>-179.1955290995776</v>
+      </c>
+      <c r="O101">
+        <v>-44.79888227489441</v>
+      </c>
+      <c r="P101">
+        <v>-134.3966468246832</v>
+      </c>
+      <c r="Q101">
+        <v>-129.7266468246832</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.552922651617733</v>
+      </c>
+      <c r="T101">
+        <v>75.10710203215646</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.05536233010151207</v>
+      </c>
+      <c r="W101">
+        <v>0.2255794755717589</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2214493204060483</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
